--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="5">
         <v>9</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6">
         <v>180</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5">
         <v>-2</v>
       </c>
       <c r="G15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6">
         <v>240</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E27" s="5">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6">
         <v>200</v>
@@ -1400,16 +1400,16 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E28" s="5">
         <v>4</v>
       </c>
       <c r="F28" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="G28" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="6">
         <v>190</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E34" s="5">
         <v>3</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H34" s="6">
         <v>200</v>
@@ -1816,16 +1816,16 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E41" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H41" s="6">
         <v>200</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E44" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5">
         <v>14</v>
@@ -2011,13 +2011,13 @@
         <v>2</v>
       </c>
       <c r="E47" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6">
         <v>240</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E50" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" s="5">
         <v>31</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E77" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
         <v>69</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
         <v>290</v>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="D91" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E91" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" s="5">
         <v>7</v>
@@ -3512,16 +3512,16 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G94" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6">
         <v>280</v>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E99" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G99" s="5">
         <v>1</v>
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="D100" s="5">
+        <v>5</v>
+      </c>
+      <c r="E100" s="5">
+        <v>4</v>
+      </c>
+      <c r="F100" s="5">
+        <v>-6</v>
+      </c>
+      <c r="G100" s="5">
         <v>7</v>
-      </c>
-      <c r="E100" s="5">
-        <v>2</v>
-      </c>
-      <c r="F100" s="5">
-        <v>-4</v>
-      </c>
-      <c r="G100" s="5">
-        <v>9</v>
       </c>
       <c r="H100" s="6">
         <v>240</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="D105" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" s="5">
         <v>2</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H105" s="6">
         <v>350</v>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="D107" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6">
         <v>340</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="5">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6">
         <v>230</v>
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E130" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5">
         <v>60</v>
       </c>
       <c r="G130" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H130" s="6">
         <v>290</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E131" s="5">
         <v>6</v>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H131" s="6">
         <v>280</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D132" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E134" s="5">
         <v>4</v>
@@ -4801,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="G134" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H134" s="6">
         <v>265</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="D137" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H147" s="6">
         <v>350</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D159" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E159" s="5">
         <v>4</v>
@@ -5601,7 +5601,7 @@
         <v>12</v>
       </c>
       <c r="G159" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H159" s="6">
         <v>400</v>
@@ -6392,16 +6392,16 @@
         </is>
       </c>
       <c r="D184" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E184" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H184" s="6">
         <v>360</v>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="D192" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E192" s="5">
         <v>4</v>
@@ -6657,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="G192" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H192" s="6">
         <v>370</v>
@@ -7064,7 +7064,7 @@
         </is>
       </c>
       <c r="D205" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E205" s="5">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H205" s="6">
         <v>380</v>
@@ -7087,16 +7087,16 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>WL215/70R15C</t>
+          <t>SP215/70R15C</t>
         </is>
       </c>
       <c r="D206" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E206" s="5">
         <v>0</v>
@@ -7105,26 +7105,26 @@
         <v>0</v>
       </c>
       <c r="G206" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H206" s="6">
-        <v>380</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>WL215/70R15C</t>
         </is>
       </c>
       <c r="D207" s="5">
@@ -7140,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="H207" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
@@ -7151,28 +7151,28 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D208" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E208" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F208" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G208" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H208" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
@@ -7183,28 +7183,28 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D209" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E209" s="5">
+        <v>1</v>
+      </c>
+      <c r="F209" s="5">
+        <v>-4</v>
+      </c>
+      <c r="G209" s="5">
         <v>2</v>
       </c>
-      <c r="E209" s="5">
-        <v>2</v>
-      </c>
-      <c r="F209" s="5">
-        <v>0</v>
-      </c>
-      <c r="G209" s="5">
-        <v>0</v>
-      </c>
       <c r="H209" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
@@ -7215,19 +7215,19 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D210" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E210" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F210" s="5">
         <v>0</v>
@@ -7236,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="H210" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D211" s="5">
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
@@ -7279,19 +7279,19 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D212" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E212" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F212" s="5">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
@@ -7311,83 +7311,83 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>RD225/40R18</t>
         </is>
       </c>
       <c r="D213" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E213" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F213" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G213" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H213" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D214" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E214" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F214" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G214" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H214" s="6">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>225/40R19</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R19</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D215" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E215" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F215" s="5">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="6">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
@@ -7407,19 +7407,19 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R19</t>
+          <t>NX225/40R19</t>
         </is>
       </c>
       <c r="D216" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E216" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F216" s="5">
         <v>0</v>
@@ -7428,30 +7428,30 @@
         <v>0</v>
       </c>
       <c r="H216" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>225/40R19RF</t>
+          <t>225/40R19</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R19RF</t>
+          <t>RD225/40R19</t>
         </is>
       </c>
       <c r="D217" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" s="5">
         <v>0</v>
@@ -7460,30 +7460,30 @@
         <v>0</v>
       </c>
       <c r="H217" s="6">
-        <v>1200</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>BR225/45R17</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D218" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="6">
-        <v>400</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>BR225/45R17</t>
         </is>
       </c>
       <c r="D219" s="5">
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="6">
-        <v>440</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
@@ -7535,28 +7535,28 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D220" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E220" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F220" s="5">
         <v>0</v>
       </c>
       <c r="G220" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
@@ -7567,28 +7567,28 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D221" s="5">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E221" s="5">
         <v>4</v>
       </c>
       <c r="F221" s="5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G221" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H221" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
@@ -7599,28 +7599,28 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D222" s="5">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E222" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F222" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G222" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H222" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
@@ -7631,19 +7631,19 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>LAUFFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D223" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" s="5">
         <v>0</v>
@@ -7652,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="H223" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
@@ -7663,22 +7663,22 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LAUFFEN</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>SP225/45R17</t>
+          <t>LF225/45R17</t>
         </is>
       </c>
       <c r="D224" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E224" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F224" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G224" s="5">
         <v>0</v>
@@ -7695,60 +7695,60 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R17</t>
+          <t>SP225/45R17</t>
         </is>
       </c>
       <c r="D225" s="5">
+        <v>12</v>
+      </c>
+      <c r="E225" s="5">
+        <v>4</v>
+      </c>
+      <c r="F225" s="5">
         <v>8</v>
       </c>
-      <c r="E225" s="5">
-        <v>4</v>
-      </c>
-      <c r="F225" s="5">
-        <v>0</v>
-      </c>
       <c r="G225" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H225" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>WL225/45R17</t>
         </is>
       </c>
       <c r="D226" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E226" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F226" s="5">
         <v>0</v>
       </c>
       <c r="G226" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H226" s="6">
-        <v>500</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
@@ -7759,28 +7759,28 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D227" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E227" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F227" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227" s="5">
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
@@ -7791,28 +7791,28 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D228" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E228" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F228" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" s="5">
         <v>0</v>
       </c>
       <c r="H228" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
@@ -7823,19 +7823,19 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D229" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E229" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F229" s="5">
         <v>0</v>
@@ -7844,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
@@ -7855,19 +7855,19 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>NX225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D230" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E230" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F230" s="5">
         <v>0</v>
@@ -7876,30 +7876,30 @@
         <v>0</v>
       </c>
       <c r="H230" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>NX225/45R18</t>
         </is>
       </c>
       <c r="D231" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" s="5">
         <v>0</v>
@@ -7908,30 +7908,30 @@
         <v>0</v>
       </c>
       <c r="H231" s="6">
-        <v>720</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D232" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F232" s="5">
         <v>0</v>
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="6">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
@@ -7951,28 +7951,28 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D233" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E233" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F233" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H233" s="6">
-        <v>750</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
@@ -7983,28 +7983,28 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D234" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E234" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F234" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H234" s="6">
-        <v>520</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
@@ -8015,19 +8015,19 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>RD225/45R19</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D235" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E235" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F235" s="5">
         <v>0</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="6">
-        <v>400</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R19</t>
+          <t>RD225/45R19</t>
         </is>
       </c>
       <c r="D236" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E236" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F236" s="5">
         <v>0</v>
@@ -8068,30 +8068,30 @@
         <v>0</v>
       </c>
       <c r="H236" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>WL225/45R19</t>
         </is>
       </c>
       <c r="D237" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E237" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F237" s="5">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
@@ -8111,28 +8111,28 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D238" s="5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E238" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F238" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G238" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H238" s="6">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
@@ -8143,60 +8143,60 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D239" s="5">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E239" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F239" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G239" s="5">
         <v>3</v>
       </c>
       <c r="H239" s="6">
-        <v>425</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D240" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E240" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F240" s="5">
         <v>0</v>
       </c>
       <c r="G240" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H240" s="6">
-        <v>450</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
@@ -8207,19 +8207,19 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D241" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E241" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F241" s="5">
         <v>0</v>
@@ -8228,23 +8228,23 @@
         <v>0</v>
       </c>
       <c r="H241" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D242" s="5">
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="H242" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17</t>
+          <t>BR225/55R17</t>
         </is>
       </c>
       <c r="D243" s="5">
@@ -8303,19 +8303,19 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17</t>
         </is>
       </c>
       <c r="D244" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E244" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F244" s="5">
         <v>0</v>
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="6">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
@@ -8335,19 +8335,19 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>RD225/55R17</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D245" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E245" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F245" s="5">
         <v>0</v>
@@ -8356,71 +8356,71 @@
         <v>0</v>
       </c>
       <c r="H245" s="6">
-        <v>360</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>RD225/55R17</t>
         </is>
       </c>
       <c r="D246" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E246" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F246" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G246" s="5">
         <v>0</v>
       </c>
       <c r="H246" s="6">
-        <v>700</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D247" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E247" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F247" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" s="5">
         <v>0</v>
       </c>
       <c r="H247" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D248" s="5">
@@ -8452,30 +8452,30 @@
         <v>0</v>
       </c>
       <c r="H248" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D249" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F249" s="5">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="H249" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="250">
@@ -8495,19 +8495,19 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D250" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E250" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F250" s="5">
         <v>0</v>
@@ -8527,19 +8527,19 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D251" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E251" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F251" s="5">
         <v>0</v>
@@ -8548,39 +8548,39 @@
         <v>0</v>
       </c>
       <c r="H251" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>225/60R16</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>BR225/60R16</t>
+          <t>HK225/55R19</t>
         </is>
       </c>
       <c r="D252" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E252" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" s="5">
         <v>0</v>
       </c>
       <c r="G252" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H252" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="253">
@@ -8591,51 +8591,51 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R16</t>
+          <t>BR225/60R16</t>
         </is>
       </c>
       <c r="D253" s="5">
         <v>2</v>
       </c>
       <c r="E253" s="5">
+        <v>0</v>
+      </c>
+      <c r="F253" s="5">
+        <v>0</v>
+      </c>
+      <c r="G253" s="5">
         <v>2</v>
       </c>
-      <c r="F253" s="5">
-        <v>0</v>
-      </c>
-      <c r="G253" s="5">
-        <v>0</v>
-      </c>
       <c r="H253" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R16</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>RD225/60R16</t>
         </is>
       </c>
       <c r="D254" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E254" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F254" s="5">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="H254" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="255">
@@ -8655,28 +8655,28 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D255" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E255" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F255" s="5">
         <v>0</v>
       </c>
       <c r="G255" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H255" s="6">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="256">
@@ -8687,28 +8687,28 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>LF225/60R17</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D256" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E256" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F256" s="5">
         <v>0</v>
       </c>
       <c r="G256" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H256" s="6">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="257">
@@ -8719,19 +8719,19 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R17</t>
+          <t>LF225/60R17</t>
         </is>
       </c>
       <c r="D257" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F257" s="5">
         <v>0</v>
@@ -8740,30 +8740,30 @@
         <v>0</v>
       </c>
       <c r="H257" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/60R17</t>
         </is>
       </c>
       <c r="D258" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F258" s="5">
         <v>0</v>
@@ -8772,30 +8772,30 @@
         <v>0</v>
       </c>
       <c r="H258" s="6">
-        <v>700</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D259" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E259" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F259" s="5">
         <v>0</v>
@@ -8804,36 +8804,36 @@
         <v>0</v>
       </c>
       <c r="H259" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D260" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E260" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F260" s="5">
         <v>0</v>
       </c>
       <c r="G260" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H260" s="6">
         <v>450</v>
@@ -8847,16 +8847,16 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D261" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E261" s="5">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="G261" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H261" s="6">
         <v>450</v>
@@ -8874,21 +8874,21 @@
     <row outlineLevel="0" r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D262" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E262" s="5">
         <v>0</v>
@@ -8897,30 +8897,30 @@
         <v>0</v>
       </c>
       <c r="G262" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H262" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>225/75R16C</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>SP225/75R16C</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D263" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" s="5">
         <v>0</v>
@@ -8929,97 +8929,97 @@
         <v>0</v>
       </c>
       <c r="G263" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" s="6">
-        <v>550</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R16C</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>SP225/75R16C</t>
         </is>
       </c>
       <c r="D264" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E264" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F264" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G264" s="5">
         <v>0</v>
       </c>
       <c r="H264" s="6">
-        <v>600</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D265" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E265" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F265" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G265" s="5">
         <v>0</v>
       </c>
       <c r="H265" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>235/45R17</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R17</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D266" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E266" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F266" s="5">
         <v>0</v>
@@ -9028,30 +9028,30 @@
         <v>0</v>
       </c>
       <c r="H266" s="6">
-        <v>420</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/45R17</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/45R17</t>
         </is>
       </c>
       <c r="D267" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E267" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F267" s="5">
         <v>0</v>
@@ -9060,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="H267" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="268">
@@ -9071,19 +9071,19 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D268" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E268" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F268" s="5">
         <v>0</v>
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="H268" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -9108,14 +9108,14 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>HK235/45R18</t>
         </is>
       </c>
       <c r="D269" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E269" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F269" s="5">
         <v>0</v>
@@ -9124,30 +9124,30 @@
         <v>0</v>
       </c>
       <c r="H269" s="6">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D270" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E270" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F270" s="5">
         <v>0</v>
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="H270" s="6">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -9172,55 +9172,55 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D271" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E271" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F271" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G271" s="5">
         <v>0</v>
       </c>
       <c r="H271" s="6">
-        <v>1180</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D272" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E272" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F272" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G272" s="5">
         <v>0</v>
       </c>
       <c r="H272" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="273">
@@ -9231,19 +9231,19 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R17</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D273" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E273" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F273" s="5">
         <v>0</v>
@@ -9258,7 +9258,7 @@
     <row outlineLevel="0" r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -9268,14 +9268,14 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>HK235/55R17</t>
         </is>
       </c>
       <c r="D274" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E274" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F274" s="5">
         <v>0</v>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="H274" s="6">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="275">
@@ -9295,19 +9295,19 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R18</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D275" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E275" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F275" s="5">
         <v>0</v>
@@ -9316,30 +9316,30 @@
         <v>0</v>
       </c>
       <c r="H275" s="6">
-        <v>400</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>RD235/55R18</t>
         </is>
       </c>
       <c r="D276" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E276" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F276" s="5">
         <v>0</v>
@@ -9348,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="H276" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="277">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D277" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F277" s="5">
         <v>0</v>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="H277" s="6">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="278">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D278" s="5">
@@ -9412,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="H278" s="6">
-        <v>550</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="279">
@@ -9423,19 +9423,19 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D279" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E279" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F279" s="5">
         <v>0</v>
@@ -9444,7 +9444,7 @@
         <v>0</v>
       </c>
       <c r="H279" s="6">
-        <v>600</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="280">
@@ -9455,19 +9455,19 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D280" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E280" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F280" s="5">
         <v>0</v>
@@ -9476,30 +9476,30 @@
         <v>0</v>
       </c>
       <c r="H280" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D281" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E281" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F281" s="5">
         <v>0</v>
@@ -9508,13 +9508,13 @@
         <v>0</v>
       </c>
       <c r="H281" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -9524,55 +9524,55 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D282" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E282" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F282" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G282" s="5">
         <v>0</v>
       </c>
       <c r="H282" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D283" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E283" s="5">
         <v>0</v>
       </c>
       <c r="F283" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G283" s="5">
         <v>0</v>
       </c>
       <c r="H283" s="6">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="284">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D284" s="5">
@@ -9604,13 +9604,13 @@
         <v>0</v>
       </c>
       <c r="H284" s="6">
-        <v>550</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>235/65R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -9620,14 +9620,14 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>HK235/65R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D285" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E285" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F285" s="5">
         <v>0</v>
@@ -9636,30 +9636,30 @@
         <v>0</v>
       </c>
       <c r="H285" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/65R17</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/65R17</t>
         </is>
       </c>
       <c r="D286" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E286" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
@@ -9668,13 +9668,13 @@
         <v>0</v>
       </c>
       <c r="H286" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -9684,87 +9684,87 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D287" s="5">
         <v>1</v>
       </c>
       <c r="E287" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" s="5">
         <v>0</v>
       </c>
       <c r="G287" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" s="6">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D288" s="5">
         <v>1</v>
       </c>
       <c r="E288" s="5">
+        <v>0</v>
+      </c>
+      <c r="F288" s="5">
+        <v>0</v>
+      </c>
+      <c r="G288" s="5">
         <v>1</v>
       </c>
-      <c r="F288" s="5">
-        <v>0</v>
-      </c>
-      <c r="G288" s="5">
-        <v>0</v>
-      </c>
       <c r="H288" s="6">
-        <v>750</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D289" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G289" s="5">
         <v>0</v>
       </c>
       <c r="H289" s="6">
-        <v>1050</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="290">
@@ -9775,44 +9775,44 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>NX245/40R20</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D290" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E290" s="5">
         <v>0</v>
       </c>
       <c r="F290" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G290" s="5">
         <v>0</v>
       </c>
       <c r="H290" s="6">
-        <v>580</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>NX245/40R20</t>
         </is>
       </c>
       <c r="D291" s="5">
@@ -9828,30 +9828,30 @@
         <v>0</v>
       </c>
       <c r="H291" s="6">
-        <v>430</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D292" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E292" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F292" s="5">
         <v>0</v>
@@ -9860,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="H292" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="293">
@@ -9871,19 +9871,19 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>BR245/45R18</t>
         </is>
       </c>
       <c r="D293" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E293" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F293" s="5">
         <v>0</v>
@@ -9892,7 +9892,7 @@
         <v>0</v>
       </c>
       <c r="H293" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="294">
@@ -9903,19 +9903,19 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D294" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E294" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F294" s="5">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="H294" s="6">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="295">
@@ -9935,19 +9935,19 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D295" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E295" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F295" s="5">
         <v>0</v>
@@ -9956,7 +9956,7 @@
         <v>0</v>
       </c>
       <c r="H295" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="296">
@@ -9967,16 +9967,16 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>LS245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D296" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296" s="5">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="G296" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H296" s="6">
         <v>500</v>
@@ -9994,21 +9994,21 @@
     <row outlineLevel="0" r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>LS245/45R18</t>
         </is>
       </c>
       <c r="D297" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E297" s="5">
         <v>0</v>
@@ -10017,26 +10017,26 @@
         <v>0</v>
       </c>
       <c r="G297" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D298" s="5">
@@ -10052,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="H298" s="6">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="299">
@@ -10063,19 +10063,19 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D299" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E299" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F299" s="5">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="H299" s="6">
-        <v>650</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="300">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R19</t>
         </is>
       </c>
       <c r="D300" s="5">
@@ -10116,23 +10116,23 @@
         <v>0</v>
       </c>
       <c r="H300" s="6">
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D301" s="5">
@@ -10148,27 +10148,27 @@
         <v>0</v>
       </c>
       <c r="H301" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D302" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E302" s="5">
         <v>0</v>
@@ -10177,30 +10177,30 @@
         <v>0</v>
       </c>
       <c r="G302" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H302" s="6">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D303" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E303" s="5">
         <v>0</v>
@@ -10209,10 +10209,10 @@
         <v>0</v>
       </c>
       <c r="G303" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H303" s="6">
-        <v>570</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="304">
@@ -10223,19 +10223,19 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>WL245/70R16</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D304" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E304" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F304" s="5">
         <v>0</v>
@@ -10244,30 +10244,30 @@
         <v>0</v>
       </c>
       <c r="H304" s="6">
-        <v>500</v>
+        <v>570</v>
       </c>
     </row>
     <row outlineLevel="0" r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>WL245/70R16</t>
         </is>
       </c>
       <c r="D305" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E305" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F305" s="5">
         <v>0</v>
@@ -10276,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="H305" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="306">
@@ -10287,19 +10287,19 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>MT255/35R19</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D306" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E306" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F306" s="5">
         <v>0</v>
@@ -10308,30 +10308,30 @@
         <v>0</v>
       </c>
       <c r="H306" s="6">
-        <v>550</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>MT255/35R19</t>
         </is>
       </c>
       <c r="D307" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" s="5">
         <v>0</v>
@@ -10340,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="H307" s="6">
-        <v>1150</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="308">
@@ -10351,19 +10351,19 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D308" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F308" s="5">
         <v>0</v>
@@ -10378,7 +10378,7 @@
     <row outlineLevel="0" r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>255/40R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -10388,14 +10388,14 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>GD255/40R20</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D309" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E309" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F309" s="5">
         <v>0</v>
@@ -10404,23 +10404,23 @@
         <v>0</v>
       </c>
       <c r="H309" s="6">
-        <v>1080</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>255/45R18</t>
+          <t>255/40R20</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>HK255/45R18</t>
+          <t>GD255/40R20</t>
         </is>
       </c>
       <c r="D310" s="5">
@@ -10436,45 +10436,45 @@
         <v>0</v>
       </c>
       <c r="H310" s="6">
-        <v>500</v>
+        <v>1080</v>
       </c>
     </row>
     <row outlineLevel="0" r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/45R18</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>HK255/45R18</t>
         </is>
       </c>
       <c r="D311" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E311" s="5">
         <v>0</v>
       </c>
       <c r="F311" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G311" s="5">
         <v>0</v>
       </c>
       <c r="H311" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -10484,29 +10484,29 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D312" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E312" s="5">
         <v>0</v>
       </c>
       <c r="F312" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G312" s="5">
         <v>0</v>
       </c>
       <c r="H312" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -10516,23 +10516,23 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D313" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E313" s="5">
         <v>0</v>
       </c>
       <c r="F313" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G313" s="5">
         <v>0</v>
       </c>
       <c r="H313" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="314">
@@ -10543,19 +10543,19 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D314" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E314" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F314" s="5">
         <v>0</v>
@@ -10564,13 +10564,13 @@
         <v>0</v>
       </c>
       <c r="H314" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -10580,14 +10580,14 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D315" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E315" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F315" s="5">
         <v>0</v>
@@ -10596,23 +10596,23 @@
         <v>0</v>
       </c>
       <c r="H315" s="6">
-        <v>550</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D316" s="5">
@@ -10628,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="H316" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="317">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>WL255/70R16</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D317" s="5">
@@ -10660,30 +10660,30 @@
         <v>0</v>
       </c>
       <c r="H317" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>WL255/70R16</t>
         </is>
       </c>
       <c r="D318" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318" s="5">
         <v>0</v>
@@ -10692,13 +10692,13 @@
         <v>0</v>
       </c>
       <c r="H318" s="6">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -10708,29 +10708,29 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D319" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E319" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F319" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G319" s="5">
         <v>0</v>
       </c>
       <c r="H319" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -10740,23 +10740,23 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>GD265/65R17</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D320" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E320" s="5">
         <v>0</v>
       </c>
       <c r="F320" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G320" s="5">
         <v>0</v>
       </c>
       <c r="H320" s="6">
-        <v>750</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="321">
@@ -10767,48 +10767,48 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>LS265/65R17</t>
+          <t>GD265/65R17</t>
         </is>
       </c>
       <c r="D321" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E321" s="5">
         <v>0</v>
       </c>
       <c r="F321" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G321" s="5">
         <v>0</v>
       </c>
       <c r="H321" s="6">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>RD265/70R16</t>
+          <t>LS265/65R17</t>
         </is>
       </c>
       <c r="D322" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E322" s="5">
         <v>0</v>
@@ -10817,176 +10817,176 @@
         <v>0</v>
       </c>
       <c r="G322" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H322" s="6">
-        <v>490</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GR265/70R16</t>
         </is>
       </c>
       <c r="D323" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E323" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F323" s="5">
         <v>0</v>
       </c>
       <c r="G323" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" s="6">
-        <v>1300</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>RD265/70R16</t>
         </is>
       </c>
       <c r="D324" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E324" s="5">
         <v>0</v>
       </c>
       <c r="F324" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G324" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H324" s="6">
-        <v>980</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D325" s="5">
         <v>2</v>
       </c>
       <c r="E325" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F325" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G325" s="5">
         <v>0</v>
       </c>
       <c r="H325" s="6">
-        <v>770</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D326" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E326" s="5">
         <v>0</v>
       </c>
       <c r="F326" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G326" s="5">
         <v>0</v>
       </c>
       <c r="H326" s="6">
-        <v>1200</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D327" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E327" s="5">
         <v>0</v>
       </c>
       <c r="F327" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G327" s="5">
         <v>0</v>
       </c>
       <c r="H327" s="6">
-        <v>900</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>275/45R21</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
@@ -10996,39 +10996,39 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>GD275/45R21</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D328" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E328" s="5">
         <v>0</v>
       </c>
       <c r="F328" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G328" s="5">
         <v>0</v>
       </c>
       <c r="H328" s="6">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/45R20</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/45R20</t>
         </is>
       </c>
       <c r="D329" s="5">
@@ -11044,109 +11044,109 @@
         <v>0</v>
       </c>
       <c r="H329" s="6">
-        <v>1300</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/45R21</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/45R21</t>
         </is>
       </c>
       <c r="D330" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E330" s="5">
         <v>0</v>
       </c>
       <c r="F330" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G330" s="5">
         <v>0</v>
       </c>
       <c r="H330" s="6">
-        <v>1600</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D331" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E331" s="5">
         <v>0</v>
       </c>
       <c r="F331" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G331" s="5">
         <v>0</v>
       </c>
       <c r="H331" s="6">
-        <v>1100</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>285/35R22</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT285/35R22</t>
         </is>
       </c>
       <c r="D332" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E332" s="5">
         <v>0</v>
       </c>
       <c r="F332" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G332" s="5">
         <v>0</v>
       </c>
       <c r="H332" s="6">
-        <v>900</v>
+        <v>1600</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -11156,54 +11156,118 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D333" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E333" s="5">
         <v>0</v>
       </c>
       <c r="F333" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G333" s="5">
         <v>0</v>
       </c>
       <c r="H333" s="6">
-        <v>1700</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D334" s="5">
+        <v>3</v>
+      </c>
+      <c r="E334" s="5">
+        <v>0</v>
+      </c>
+      <c r="F334" s="5">
+        <v>3</v>
+      </c>
+      <c r="G334" s="5">
+        <v>0</v>
+      </c>
+      <c r="H334" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="335">
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D335" s="5">
+        <v>0</v>
+      </c>
+      <c r="E335" s="5">
+        <v>0</v>
+      </c>
+      <c r="F335" s="5">
+        <v>0</v>
+      </c>
+      <c r="G335" s="5">
+        <v>0</v>
+      </c>
+      <c r="H335" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B334" s="4" t="inlineStr">
+      <c r="B336" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C334" s="4" t="inlineStr">
+      <c r="C336" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D334" s="5">
+      <c r="D336" s="5">
         <v>2</v>
       </c>
-      <c r="E334" s="5">
+      <c r="E336" s="5">
         <v>2</v>
       </c>
-      <c r="F334" s="5">
-        <v>0</v>
-      </c>
-      <c r="G334" s="5">
-        <v>0</v>
-      </c>
-      <c r="H334" s="6">
+      <c r="F336" s="5">
+        <v>0</v>
+      </c>
+      <c r="G336" s="5">
+        <v>0</v>
+      </c>
+      <c r="H336" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H336"/>
+  <dimension ref="A1:H338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5">
         <v>-2</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="5">
         <v>3</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E28" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="5">
         <v>-1</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E44" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5">
         <v>14</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E64" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5">
         <v>81</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E68" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5">
         <v>9</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E89" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D113" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5">
         <v>3</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="D137" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="D150" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -6095,19 +6095,19 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>HK215/55R16</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E175" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
@@ -6127,16 +6127,16 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>RD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E176" s="5">
         <v>0</v>
@@ -6145,33 +6145,33 @@
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>RD215/55R16</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>4</v>
       </c>
       <c r="H177" s="6">
-        <v>480</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
@@ -6191,28 +6191,28 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E178" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H178" s="6">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
@@ -6223,19 +6223,19 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R17</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E179" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>2</v>
       </c>
       <c r="H179" s="6">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,92 +6255,92 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>SP215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E180" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
       </c>
       <c r="G180" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H180" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>SP215/55R17</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E181" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F182" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="6">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
@@ -6383,28 +6383,28 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
@@ -6415,51 +6415,51 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H185" s="6">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>DS215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
@@ -6468,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
@@ -6479,28 +6479,28 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD215/60R17</t>
+          <t>DS215/60R17</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F187" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>520</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
@@ -6511,28 +6511,28 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R17</t>
+          <t>GD215/60R17</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E188" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F188" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H188" s="6">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
@@ -6543,19 +6543,19 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>HK215/60R17</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E189" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F189" s="5">
         <v>0</v>
@@ -6564,39 +6564,39 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>BR215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E190" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F190" s="5">
         <v>0</v>
       </c>
       <c r="G190" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
@@ -6607,28 +6607,28 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>BR215/65R16</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E191" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F191" s="5">
         <v>0</v>
       </c>
       <c r="G191" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H191" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
@@ -6639,28 +6639,28 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D192" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E192" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F192" s="5">
         <v>0</v>
       </c>
       <c r="G192" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
@@ -6671,28 +6671,28 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>LF215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E193" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
       </c>
       <c r="G193" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H193" s="6">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>RD215/65R16</t>
+          <t>LF215/65R16</t>
         </is>
       </c>
       <c r="D194" s="5">
@@ -6724,30 +6724,30 @@
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R17</t>
+          <t>RD215/65R16</t>
         </is>
       </c>
       <c r="D195" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E195" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F195" s="5">
         <v>0</v>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>480</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
@@ -6767,19 +6767,19 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R17</t>
         </is>
       </c>
       <c r="D196" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E196" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F196" s="5">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
@@ -6799,19 +6799,19 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>NX215/65R17</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D197" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" s="5">
         <v>0</v>
@@ -6820,23 +6820,23 @@
         <v>0</v>
       </c>
       <c r="H197" s="6">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>215/70R15</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15</t>
+          <t>NX215/65R17</t>
         </is>
       </c>
       <c r="D198" s="5">
@@ -6852,23 +6852,23 @@
         <v>0</v>
       </c>
       <c r="H198" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/70R15</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>AM215/70R15C</t>
+          <t>RD215/70R15</t>
         </is>
       </c>
       <c r="D199" s="5">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>BM215/70R15C</t>
+          <t>AM215/70R15C</t>
         </is>
       </c>
       <c r="D200" s="5">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>DS215/70R15C</t>
+          <t>BM215/70R15C</t>
         </is>
       </c>
       <c r="D201" s="5">
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="202">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>DS215/70R15C</t>
         </is>
       </c>
       <c r="D202" s="5">
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="6">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
@@ -6991,28 +6991,28 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>MC215/70R15C</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D203" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E203" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F203" s="5">
         <v>0</v>
       </c>
       <c r="G203" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H203" s="6">
-        <v>600</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="204">
@@ -7023,28 +7023,28 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>OVASION</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>OV215/70R15C</t>
+          <t>MC215/70R15C</t>
         </is>
       </c>
       <c r="D204" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E204" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F204" s="5">
         <v>0</v>
       </c>
       <c r="G204" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H204" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
@@ -7055,16 +7055,16 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>OVASION</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>OV215/70R15C</t>
         </is>
       </c>
       <c r="D205" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E205" s="5">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H205" s="6">
         <v>380</v>
@@ -7087,16 +7087,16 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>SP215/70R15C</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D206" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E206" s="5">
         <v>0</v>
@@ -7105,10 +7105,10 @@
         <v>0</v>
       </c>
       <c r="G206" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H206" s="6">
-        <v>490</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
@@ -7119,16 +7119,16 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>WL215/70R15C</t>
+          <t>SP215/70R15C</t>
         </is>
       </c>
       <c r="D207" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E207" s="5">
         <v>0</v>
@@ -7137,26 +7137,26 @@
         <v>0</v>
       </c>
       <c r="G207" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H207" s="6">
-        <v>380</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>WL215/70R15C</t>
         </is>
       </c>
       <c r="D208" s="5">
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="H208" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
@@ -7183,28 +7183,28 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D209" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E209" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F209" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G209" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H209" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
@@ -7215,28 +7215,28 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D210" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E210" s="5">
+        <v>1</v>
+      </c>
+      <c r="F210" s="5">
+        <v>-4</v>
+      </c>
+      <c r="G210" s="5">
         <v>2</v>
       </c>
-      <c r="E210" s="5">
-        <v>2</v>
-      </c>
-      <c r="F210" s="5">
-        <v>0</v>
-      </c>
-      <c r="G210" s="5">
-        <v>0</v>
-      </c>
       <c r="H210" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
@@ -7247,19 +7247,19 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D211" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E211" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F211" s="5">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="H211" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D212" s="5">
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
@@ -7311,19 +7311,19 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D213" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E213" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F213" s="5">
         <v>0</v>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
@@ -7343,83 +7343,83 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>RD225/40R18</t>
         </is>
       </c>
       <c r="D214" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E214" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F214" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G214" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H214" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D215" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E215" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F215" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G215" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H215" s="6">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>225/40R19</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R19</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D216" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E216" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F216" s="5">
         <v>0</v>
@@ -7428,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="H216" s="6">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
@@ -7439,19 +7439,19 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R19</t>
+          <t>NX225/40R19</t>
         </is>
       </c>
       <c r="D217" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E217" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F217" s="5">
         <v>0</v>
@@ -7460,30 +7460,30 @@
         <v>0</v>
       </c>
       <c r="H217" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>225/40R19RF</t>
+          <t>225/40R19</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R19RF</t>
+          <t>RD225/40R19</t>
         </is>
       </c>
       <c r="D218" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
@@ -7492,30 +7492,30 @@
         <v>0</v>
       </c>
       <c r="H218" s="6">
-        <v>1200</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>BR225/45R17</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D219" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" s="5">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="6">
-        <v>400</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>BR225/45R17</t>
         </is>
       </c>
       <c r="D220" s="5">
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>440</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
@@ -7567,28 +7567,28 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D221" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E221" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F221" s="5">
         <v>0</v>
       </c>
       <c r="G221" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H221" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
@@ -7599,28 +7599,28 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D222" s="5">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E222" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F222" s="5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G222" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H222" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
@@ -7631,28 +7631,28 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D223" s="5">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E223" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F223" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G223" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H223" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
@@ -7663,19 +7663,19 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>LAUFFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D224" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" s="5">
         <v>0</v>
@@ -7684,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="H224" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
@@ -7695,22 +7695,22 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LAUFFEN</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>SP225/45R17</t>
+          <t>LF225/45R17</t>
         </is>
       </c>
       <c r="D225" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E225" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F225" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G225" s="5">
         <v>0</v>
@@ -7727,92 +7727,92 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R17</t>
+          <t>RD225/45R17</t>
         </is>
       </c>
       <c r="D226" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E226" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F226" s="5">
         <v>0</v>
       </c>
       <c r="G226" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H226" s="6">
-        <v>330</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>SP225/45R17</t>
         </is>
       </c>
       <c r="D227" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E227" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F227" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G227" s="5">
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>WL225/45R17</t>
         </is>
       </c>
       <c r="D228" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E228" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F228" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H228" s="6">
-        <v>550</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
@@ -7823,19 +7823,19 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D229" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" s="5">
         <v>0</v>
@@ -7844,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="H229" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D230" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E230" s="5">
         <v>4</v>
       </c>
       <c r="F230" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G230" s="5">
         <v>0</v>
       </c>
       <c r="H230" s="6">
-        <v>420</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
@@ -7887,19 +7887,19 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>NX225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D231" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F231" s="5">
         <v>0</v>
@@ -7914,24 +7914,24 @@
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D232" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E232" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F232" s="5">
         <v>0</v>
@@ -7940,23 +7940,23 @@
         <v>0</v>
       </c>
       <c r="H232" s="6">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>NX225/45R18</t>
         </is>
       </c>
       <c r="D233" s="5">
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H233" s="6">
-        <v>780</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -7988,23 +7988,23 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D234" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E234" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F234" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G234" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H234" s="6">
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
@@ -8015,19 +8015,19 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D235" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E235" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" s="5">
         <v>0</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="6">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
@@ -8047,28 +8047,28 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>RD225/45R19</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D236" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E236" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F236" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H236" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
@@ -8079,19 +8079,19 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R19</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D237" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E237" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F237" s="5">
         <v>0</v>
@@ -8100,30 +8100,30 @@
         <v>0</v>
       </c>
       <c r="H237" s="6">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>RD225/45R19</t>
         </is>
       </c>
       <c r="D238" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E238" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F238" s="5">
         <v>0</v>
@@ -8132,39 +8132,39 @@
         <v>0</v>
       </c>
       <c r="H238" s="6">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>WL225/45R19</t>
         </is>
       </c>
       <c r="D239" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E239" s="5">
         <v>4</v>
       </c>
       <c r="F239" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G239" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H239" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
@@ -8175,80 +8175,80 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D240" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E240" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" s="5">
         <v>0</v>
       </c>
       <c r="G240" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H240" s="6">
-        <v>425</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D241" s="5">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E241" s="5">
         <v>4</v>
       </c>
       <c r="F241" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G241" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H241" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D242" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E242" s="5">
         <v>0</v>
@@ -8257,33 +8257,33 @@
         <v>0</v>
       </c>
       <c r="G242" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H242" s="6">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D243" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E243" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F243" s="5">
         <v>0</v>
@@ -8292,13 +8292,13 @@
         <v>0</v>
       </c>
       <c r="H243" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D244" s="5">
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="H244" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
@@ -8335,19 +8335,19 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>BR225/55R17</t>
         </is>
       </c>
       <c r="D245" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E245" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F245" s="5">
         <v>0</v>
@@ -8356,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="H245" s="6">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
@@ -8367,19 +8367,19 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>RD225/55R17</t>
+          <t>GD225/55R17</t>
         </is>
       </c>
       <c r="D246" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" s="5">
         <v>0</v>
@@ -8388,62 +8388,62 @@
         <v>0</v>
       </c>
       <c r="H246" s="6">
-        <v>360</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D247" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E247" s="5">
         <v>4</v>
       </c>
       <c r="F247" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247" s="5">
         <v>0</v>
       </c>
       <c r="H247" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>RD225/55R17</t>
         </is>
       </c>
       <c r="D248" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F248" s="5">
         <v>0</v>
@@ -8452,62 +8452,62 @@
         <v>0</v>
       </c>
       <c r="H248" s="6">
-        <v>500</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D249" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E249" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F249" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" s="5">
         <v>0</v>
       </c>
       <c r="H249" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D250" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E250" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F250" s="5">
         <v>0</v>
@@ -8516,30 +8516,30 @@
         <v>0</v>
       </c>
       <c r="H250" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D251" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E251" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F251" s="5">
         <v>0</v>
@@ -8548,7 +8548,7 @@
         <v>0</v>
       </c>
       <c r="H251" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="252">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D252" s="5">
@@ -8580,62 +8580,62 @@
         <v>0</v>
       </c>
       <c r="H252" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>225/60R16</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>BR225/60R16</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D253" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E253" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F253" s="5">
         <v>0</v>
       </c>
       <c r="G253" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H253" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>225/60R16</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R16</t>
+          <t>HK225/55R19</t>
         </is>
       </c>
       <c r="D254" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F254" s="5">
         <v>0</v>
@@ -8644,27 +8644,27 @@
         <v>0</v>
       </c>
       <c r="H254" s="6">
-        <v>350</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R16</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>BR225/60R16</t>
         </is>
       </c>
       <c r="D255" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E255" s="5">
         <v>0</v>
@@ -8673,42 +8673,42 @@
         <v>0</v>
       </c>
       <c r="G255" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H255" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R16</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>RD225/60R16</t>
         </is>
       </c>
       <c r="D256" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E256" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F256" s="5">
         <v>0</v>
       </c>
       <c r="G256" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H256" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="257">
@@ -8719,19 +8719,19 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>LF225/60R17</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D257" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E257" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F257" s="5">
         <v>0</v>
@@ -8740,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="H257" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="258">
@@ -8751,44 +8751,44 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R17</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D258" s="5">
+        <v>6</v>
+      </c>
+      <c r="E258" s="5">
+        <v>4</v>
+      </c>
+      <c r="F258" s="5">
+        <v>0</v>
+      </c>
+      <c r="G258" s="5">
         <v>2</v>
       </c>
-      <c r="E258" s="5">
-        <v>2</v>
-      </c>
-      <c r="F258" s="5">
-        <v>0</v>
-      </c>
-      <c r="G258" s="5">
-        <v>0</v>
-      </c>
       <c r="H258" s="6">
-        <v>300</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>LF225/60R17</t>
         </is>
       </c>
       <c r="D259" s="5">
@@ -8804,13 +8804,13 @@
         <v>0</v>
       </c>
       <c r="H259" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -8820,14 +8820,14 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/60R17</t>
         </is>
       </c>
       <c r="D260" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E260" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F260" s="5">
         <v>0</v>
@@ -8836,68 +8836,68 @@
         <v>0</v>
       </c>
       <c r="H260" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D261" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E261" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F261" s="5">
         <v>0</v>
       </c>
       <c r="G261" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H261" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D262" s="5">
         <v>3</v>
       </c>
       <c r="E262" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F262" s="5">
         <v>0</v>
       </c>
       <c r="G262" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H262" s="6">
         <v>450</v>
@@ -8906,21 +8906,21 @@
     <row outlineLevel="0" r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D263" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E263" s="5">
         <v>0</v>
@@ -8929,16 +8929,16 @@
         <v>0</v>
       </c>
       <c r="G263" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H263" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>225/75R16C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>SP225/75R16C</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D264" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E264" s="5">
         <v>0</v>
@@ -8961,16 +8961,16 @@
         <v>0</v>
       </c>
       <c r="G264" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H264" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -8980,46 +8980,46 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D265" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E265" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F265" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G265" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/75R16C</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>SP225/75R16C</t>
         </is>
       </c>
       <c r="D266" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E266" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F266" s="5">
         <v>0</v>
@@ -9028,45 +9028,45 @@
         <v>0</v>
       </c>
       <c r="H266" s="6">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>235/45R17</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R17</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D267" s="5">
         <v>4</v>
       </c>
       <c r="E267" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F267" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G267" s="5">
         <v>0</v>
       </c>
       <c r="H267" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D268" s="5">
@@ -9092,13 +9092,13 @@
         <v>0</v>
       </c>
       <c r="H268" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/45R17</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -9108,14 +9108,14 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R18</t>
+          <t>HK235/45R17</t>
         </is>
       </c>
       <c r="D269" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E269" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F269" s="5">
         <v>0</v>
@@ -9124,30 +9124,30 @@
         <v>0</v>
       </c>
       <c r="H269" s="6">
-        <v>500</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D270" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E270" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F270" s="5">
         <v>0</v>
@@ -9156,30 +9156,30 @@
         <v>0</v>
       </c>
       <c r="H270" s="6">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/45R18</t>
         </is>
       </c>
       <c r="D271" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E271" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F271" s="5">
         <v>0</v>
@@ -9188,62 +9188,62 @@
         <v>0</v>
       </c>
       <c r="H271" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D272" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E272" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F272" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G272" s="5">
         <v>0</v>
       </c>
       <c r="H272" s="6">
-        <v>1180</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D273" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E273" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F273" s="5">
         <v>0</v>
@@ -9252,62 +9252,62 @@
         <v>0</v>
       </c>
       <c r="H273" s="6">
-        <v>450</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D274" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E274" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F274" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G274" s="5">
         <v>0</v>
       </c>
       <c r="H274" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D275" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E275" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F275" s="5">
         <v>0</v>
@@ -9316,30 +9316,30 @@
         <v>0</v>
       </c>
       <c r="H275" s="6">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R18</t>
+          <t>HK235/55R17</t>
         </is>
       </c>
       <c r="D276" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E276" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F276" s="5">
         <v>0</v>
@@ -9348,30 +9348,30 @@
         <v>0</v>
       </c>
       <c r="H276" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D277" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E277" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F277" s="5">
         <v>0</v>
@@ -9380,23 +9380,23 @@
         <v>0</v>
       </c>
       <c r="H277" s="6">
-        <v>750</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>RD235/55R18</t>
         </is>
       </c>
       <c r="D278" s="5">
@@ -9412,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="H278" s="6">
-        <v>630</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="279">
@@ -9423,19 +9423,19 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D279" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F279" s="5">
         <v>0</v>
@@ -9444,7 +9444,7 @@
         <v>0</v>
       </c>
       <c r="H279" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="280">
@@ -9455,19 +9455,19 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D280" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E280" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" s="5">
         <v>0</v>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="H280" s="6">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="281">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D281" s="5">
@@ -9508,30 +9508,30 @@
         <v>0</v>
       </c>
       <c r="H281" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D282" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E282" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F282" s="5">
         <v>0</v>
@@ -9540,33 +9540,33 @@
         <v>0</v>
       </c>
       <c r="H282" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D283" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E283" s="5">
         <v>0</v>
       </c>
       <c r="F283" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G283" s="5">
         <v>0</v>
@@ -9578,24 +9578,24 @@
     <row outlineLevel="0" r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D284" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E284" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F284" s="5">
         <v>0</v>
@@ -9604,13 +9604,13 @@
         <v>0</v>
       </c>
       <c r="H284" s="6">
-        <v>680</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -9620,46 +9620,46 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D285" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E285" s="5">
         <v>0</v>
       </c>
       <c r="F285" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G285" s="5">
         <v>0</v>
       </c>
       <c r="H285" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>235/65R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>HK235/65R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D286" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E286" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
@@ -9668,30 +9668,30 @@
         <v>0</v>
       </c>
       <c r="H286" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D287" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F287" s="5">
         <v>0</v>
@@ -9700,55 +9700,55 @@
         <v>0</v>
       </c>
       <c r="H287" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/65R17</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/65R17</t>
         </is>
       </c>
       <c r="D288" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E288" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F288" s="5">
         <v>0</v>
       </c>
       <c r="G288" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H288" s="6">
-        <v>620</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D289" s="5">
@@ -9764,55 +9764,55 @@
         <v>0</v>
       </c>
       <c r="H289" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D290" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E290" s="5">
         <v>0</v>
       </c>
       <c r="F290" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G290" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H290" s="6">
-        <v>1050</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>NX245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D291" s="5">
@@ -9828,62 +9828,62 @@
         <v>0</v>
       </c>
       <c r="H291" s="6">
-        <v>580</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D292" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E292" s="5">
         <v>0</v>
       </c>
       <c r="F292" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G292" s="5">
         <v>0</v>
       </c>
       <c r="H292" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R18</t>
+          <t>NX245/40R20</t>
         </is>
       </c>
       <c r="D293" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E293" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F293" s="5">
         <v>0</v>
@@ -9892,30 +9892,30 @@
         <v>0</v>
       </c>
       <c r="H293" s="6">
-        <v>600</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D294" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E294" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" s="5">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="H294" s="6">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="295">
@@ -9935,19 +9935,19 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>BR245/45R18</t>
         </is>
       </c>
       <c r="D295" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E295" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F295" s="5">
         <v>0</v>
@@ -9967,19 +9967,19 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D296" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F296" s="5">
         <v>0</v>
@@ -9988,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="H296" s="6">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="297">
@@ -9999,44 +9999,44 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>LS245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D297" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E297" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F297" s="5">
         <v>0</v>
       </c>
       <c r="G297" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H297" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D298" s="5">
@@ -10052,27 +10052,27 @@
         <v>0</v>
       </c>
       <c r="H298" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>LS245/45R18</t>
         </is>
       </c>
       <c r="D299" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" s="5">
         <v>0</v>
@@ -10081,26 +10081,26 @@
         <v>0</v>
       </c>
       <c r="G299" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H299" s="6">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D300" s="5">
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="H300" s="6">
-        <v>650</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="301">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D301" s="5">
@@ -10148,13 +10148,13 @@
         <v>0</v>
       </c>
       <c r="H301" s="6">
-        <v>450</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>HK245/45R19</t>
         </is>
       </c>
       <c r="D302" s="5">
@@ -10180,27 +10180,27 @@
         <v>0</v>
       </c>
       <c r="H302" s="6">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D303" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E303" s="5">
         <v>0</v>
@@ -10209,26 +10209,26 @@
         <v>0</v>
       </c>
       <c r="G303" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H303" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D304" s="5">
@@ -10244,55 +10244,55 @@
         <v>0</v>
       </c>
       <c r="H304" s="6">
-        <v>570</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>WL245/70R16</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D305" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E305" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F305" s="5">
         <v>0</v>
       </c>
       <c r="G305" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H305" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D306" s="5">
@@ -10308,30 +10308,30 @@
         <v>0</v>
       </c>
       <c r="H306" s="6">
-        <v>700</v>
+        <v>570</v>
       </c>
     </row>
     <row outlineLevel="0" r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>MT255/35R19</t>
+          <t>WL245/70R16</t>
         </is>
       </c>
       <c r="D307" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E307" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F307" s="5">
         <v>0</v>
@@ -10340,23 +10340,23 @@
         <v>0</v>
       </c>
       <c r="H307" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D308" s="5">
@@ -10372,23 +10372,23 @@
         <v>0</v>
       </c>
       <c r="H308" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>MT255/35R19</t>
         </is>
       </c>
       <c r="D309" s="5">
@@ -10404,23 +10404,23 @@
         <v>0</v>
       </c>
       <c r="H309" s="6">
-        <v>1150</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>255/40R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>GD255/40R20</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D310" s="5">
@@ -10436,30 +10436,30 @@
         <v>0</v>
       </c>
       <c r="H310" s="6">
-        <v>1080</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>255/45R18</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>HK255/45R18</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D311" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F311" s="5">
         <v>0</v>
@@ -10468,77 +10468,77 @@
         <v>0</v>
       </c>
       <c r="H311" s="6">
-        <v>500</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/40R20</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/40R20</t>
         </is>
       </c>
       <c r="D312" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E312" s="5">
         <v>0</v>
       </c>
       <c r="F312" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G312" s="5">
         <v>0</v>
       </c>
       <c r="H312" s="6">
-        <v>750</v>
+        <v>1080</v>
       </c>
     </row>
     <row outlineLevel="0" r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/45R18</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>HK255/45R18</t>
         </is>
       </c>
       <c r="D313" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E313" s="5">
         <v>0</v>
       </c>
       <c r="F313" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G313" s="5">
         <v>0</v>
       </c>
       <c r="H313" s="6">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -10548,17 +10548,17 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D314" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E314" s="5">
         <v>0</v>
       </c>
       <c r="F314" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G314" s="5">
         <v>0</v>
@@ -10570,49 +10570,49 @@
     <row outlineLevel="0" r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D315" s="5">
         <v>2</v>
       </c>
       <c r="E315" s="5">
+        <v>0</v>
+      </c>
+      <c r="F315" s="5">
         <v>2</v>
       </c>
-      <c r="F315" s="5">
-        <v>0</v>
-      </c>
       <c r="G315" s="5">
         <v>0</v>
       </c>
       <c r="H315" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D316" s="5">
@@ -10628,30 +10628,30 @@
         <v>0</v>
       </c>
       <c r="H316" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D317" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E317" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F317" s="5">
         <v>0</v>
@@ -10660,23 +10660,23 @@
         <v>0</v>
       </c>
       <c r="H317" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>WL255/70R16</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D318" s="5">
@@ -10698,24 +10698,24 @@
     <row outlineLevel="0" r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D319" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E319" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F319" s="5">
         <v>0</v>
@@ -10724,45 +10724,45 @@
         <v>0</v>
       </c>
       <c r="H319" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>WL255/70R16</t>
         </is>
       </c>
       <c r="D320" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E320" s="5">
         <v>0</v>
       </c>
       <c r="F320" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G320" s="5">
         <v>0</v>
       </c>
       <c r="H320" s="6">
-        <v>1150</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -10772,107 +10772,107 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>GD265/65R17</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D321" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E321" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F321" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G321" s="5">
         <v>0</v>
       </c>
       <c r="H321" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>LS265/65R17</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D322" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E322" s="5">
         <v>0</v>
       </c>
       <c r="F322" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G322" s="5">
         <v>0</v>
       </c>
       <c r="H322" s="6">
-        <v>650</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>GR265/70R16</t>
+          <t>GD265/65R17</t>
         </is>
       </c>
       <c r="D323" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E323" s="5">
         <v>0</v>
       </c>
       <c r="F323" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G323" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H323" s="6">
-        <v>490</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>RD265/70R16</t>
+          <t>LS265/65R17</t>
         </is>
       </c>
       <c r="D324" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E324" s="5">
         <v>0</v>
@@ -10881,176 +10881,176 @@
         <v>0</v>
       </c>
       <c r="G324" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H324" s="6">
-        <v>490</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GR265/70R16</t>
         </is>
       </c>
       <c r="D325" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E325" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F325" s="5">
         <v>0</v>
       </c>
       <c r="G325" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H325" s="6">
-        <v>1300</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>RD265/70R16</t>
         </is>
       </c>
       <c r="D326" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E326" s="5">
         <v>0</v>
       </c>
       <c r="F326" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G326" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H326" s="6">
-        <v>980</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D327" s="5">
         <v>2</v>
       </c>
       <c r="E327" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F327" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G327" s="5">
         <v>0</v>
       </c>
       <c r="H327" s="6">
-        <v>770</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D328" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E328" s="5">
         <v>0</v>
       </c>
       <c r="F328" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G328" s="5">
         <v>0</v>
       </c>
       <c r="H328" s="6">
-        <v>1200</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D329" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E329" s="5">
         <v>0</v>
       </c>
       <c r="F329" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G329" s="5">
         <v>0</v>
       </c>
       <c r="H329" s="6">
-        <v>900</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>275/45R21</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
@@ -11060,39 +11060,39 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>GD275/45R21</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D330" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E330" s="5">
         <v>0</v>
       </c>
       <c r="F330" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G330" s="5">
         <v>0</v>
       </c>
       <c r="H330" s="6">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/45R20</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/45R20</t>
         </is>
       </c>
       <c r="D331" s="5">
@@ -11108,109 +11108,109 @@
         <v>0</v>
       </c>
       <c r="H331" s="6">
-        <v>1300</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/45R21</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/45R21</t>
         </is>
       </c>
       <c r="D332" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E332" s="5">
         <v>0</v>
       </c>
       <c r="F332" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G332" s="5">
         <v>0</v>
       </c>
       <c r="H332" s="6">
-        <v>1600</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D333" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E333" s="5">
         <v>0</v>
       </c>
       <c r="F333" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G333" s="5">
         <v>0</v>
       </c>
       <c r="H333" s="6">
-        <v>1100</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>285/35R22</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT285/35R22</t>
         </is>
       </c>
       <c r="D334" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E334" s="5">
         <v>0</v>
       </c>
       <c r="F334" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G334" s="5">
         <v>0</v>
       </c>
       <c r="H334" s="6">
-        <v>900</v>
+        <v>1600</v>
       </c>
     </row>
     <row outlineLevel="0" r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
@@ -11220,54 +11220,118 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D335" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E335" s="5">
         <v>0</v>
       </c>
       <c r="F335" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G335" s="5">
         <v>0</v>
       </c>
       <c r="H335" s="6">
-        <v>1700</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D336" s="5">
+        <v>3</v>
+      </c>
+      <c r="E336" s="5">
+        <v>0</v>
+      </c>
+      <c r="F336" s="5">
+        <v>3</v>
+      </c>
+      <c r="G336" s="5">
+        <v>0</v>
+      </c>
+      <c r="H336" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="337">
+      <c r="A337" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D337" s="5">
+        <v>0</v>
+      </c>
+      <c r="E337" s="5">
+        <v>0</v>
+      </c>
+      <c r="F337" s="5">
+        <v>0</v>
+      </c>
+      <c r="G337" s="5">
+        <v>0</v>
+      </c>
+      <c r="H337" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="338">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B336" s="4" t="inlineStr">
+      <c r="B338" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C336" s="4" t="inlineStr">
+      <c r="C338" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D336" s="5">
+      <c r="D338" s="5">
         <v>2</v>
       </c>
-      <c r="E336" s="5">
+      <c r="E338" s="5">
         <v>2</v>
       </c>
-      <c r="F336" s="5">
-        <v>0</v>
-      </c>
-      <c r="G336" s="5">
-        <v>0</v>
-      </c>
-      <c r="H336" s="6">
+      <c r="F338" s="5">
+        <v>0</v>
+      </c>
+      <c r="G338" s="5">
+        <v>0</v>
+      </c>
+      <c r="H338" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5">
         <v>4</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E27" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F27" s="5">
         <v>8</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F28" s="5">
         <v>-1</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E34" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5">
         <v>0</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E41" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" s="5">
         <v>14</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E49" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E64" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="5">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G64" s="5">
         <v>4</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E69" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F69" s="5">
         <v>23</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F94" s="5">
         <v>14</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="D98" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E99" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" s="5">
         <v>38</v>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="G100" s="5">
         <v>7</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E114" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5">
         <v>5</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="E119" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G119" s="5">
         <v>0</v>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F130" s="5">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G130" s="5">
         <v>10</v>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E134" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5">
         <v>16</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E135" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E146" s="5">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F146" s="5">
         <v>1</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="D151" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5400,10 +5400,10 @@
         </is>
       </c>
       <c r="D153" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5787,10 +5787,10 @@
         <v>2</v>
       </c>
       <c r="E165" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F165" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D182" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E182" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F182" s="5">
         <v>-1</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D193" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D211" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E211" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F211" s="5">
         <v>0</v>
@@ -7608,10 +7608,10 @@
         </is>
       </c>
       <c r="D222" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E222" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F222" s="5">
         <v>0</v>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="D223" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E223" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F223" s="5">
         <v>18</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D243" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E243" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F243" s="5">
         <v>0</v>
@@ -8920,10 +8920,10 @@
         </is>
       </c>
       <c r="D263" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E263" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F263" s="5">
         <v>0</v>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D267" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E267" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F267" s="5">
         <v>2</v>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D284" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E284" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F284" s="5">
         <v>0</v>
@@ -9787,10 +9787,10 @@
         <v>1</v>
       </c>
       <c r="E290" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F290" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G290" s="5">
         <v>1</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E119" s="5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F119" s="5">
         <v>-4</v>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E165" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F165" s="5">
         <v>-4</v>
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D182" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F182" s="5">
         <v>-1</v>
@@ -9656,10 +9656,10 @@
         </is>
       </c>
       <c r="D286" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E286" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D290" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E290" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F290" s="5">
         <v>-4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5">
         <v>-2</v>
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5">
         <v>-2</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E24" s="5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F24" s="5">
         <v>0</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E27" s="5">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="F27" s="5">
         <v>8</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E41" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E58" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" s="5">
         <v>9</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E69" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5">
         <v>23</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="D72" s="5">
+        <v>4</v>
+      </c>
+      <c r="E72" s="5">
         <v>3</v>
-      </c>
-      <c r="E72" s="5">
-        <v>2</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
         <v>-9</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="D16" s="5">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5">
         <v>2</v>
-      </c>
-      <c r="E16" s="5">
-        <v>-1</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E27" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F27" s="5">
         <v>8</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5">
         <v>0</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E64" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F64" s="5">
         <v>75</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E94" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F94" s="5">
         <v>14</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E95" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E99" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
         <v>38</v>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="D109" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E114" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="5">
         <v>5</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E119" s="5">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5">
         <v>-4</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="D128" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E130" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F130" s="5">
         <v>52</v>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E134" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5">
         <v>16</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E135" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="D150" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="D152" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D165" s="5">
+        <v>2</v>
+      </c>
+      <c r="E165" s="5">
         <v>6</v>
-      </c>
-      <c r="E165" s="5">
-        <v>10</v>
       </c>
       <c r="F165" s="5">
         <v>-4</v>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="D169" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="D178" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E178" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="D179" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E179" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F182" s="5">
         <v>-1</v>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="D188" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E188" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188" s="5">
         <v>1</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="D193" s="5">
+        <v>5</v>
+      </c>
+      <c r="E193" s="5">
         <v>3</v>
-      </c>
-      <c r="E193" s="5">
-        <v>1</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="D207" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E207" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F207" s="5">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D214" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E214" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F214" s="5">
         <v>0</v>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="D223" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E223" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F223" s="5">
         <v>18</v>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D267" s="5">
+        <v>4</v>
+      </c>
+      <c r="E267" s="5">
         <v>2</v>
-      </c>
-      <c r="E267" s="5">
-        <v>0</v>
       </c>
       <c r="F267" s="5">
         <v>2</v>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="D288" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E288" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F288" s="5">
         <v>0</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D290" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E290" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F290" s="5">
         <v>-4</v>
@@ -10328,10 +10328,10 @@
         </is>
       </c>
       <c r="D307" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E307" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F307" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H339"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E64" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F64" s="5">
         <v>75</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="5">
         <v>-4</v>
@@ -10890,33 +10890,33 @@
     <row outlineLevel="0" r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>GR265/70R16</t>
+          <t>NX265/65R17</t>
         </is>
       </c>
       <c r="D325" s="5">
+        <v>5</v>
+      </c>
+      <c r="E325" s="5">
         <v>1</v>
       </c>
-      <c r="E325" s="5">
-        <v>0</v>
-      </c>
       <c r="F325" s="5">
         <v>0</v>
       </c>
       <c r="G325" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H325" s="6">
-        <v>490</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
@@ -10927,16 +10927,16 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>RD265/70R16</t>
+          <t>GR265/70R16</t>
         </is>
       </c>
       <c r="D326" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E326" s="5">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H326" s="6">
         <v>490</v>
@@ -10954,81 +10954,81 @@
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>RD265/70R16</t>
         </is>
       </c>
       <c r="D327" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E327" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F327" s="5">
         <v>0</v>
       </c>
       <c r="G327" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H327" s="6">
-        <v>1300</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D328" s="5">
         <v>2</v>
       </c>
       <c r="E328" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F328" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G328" s="5">
         <v>0</v>
       </c>
       <c r="H328" s="6">
-        <v>980</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D329" s="5">
@@ -11044,55 +11044,55 @@
         <v>0</v>
       </c>
       <c r="H329" s="6">
-        <v>770</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D330" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E330" s="5">
         <v>0</v>
       </c>
       <c r="F330" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G330" s="5">
         <v>0</v>
       </c>
       <c r="H330" s="6">
-        <v>1200</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D331" s="5">
@@ -11108,45 +11108,45 @@
         <v>0</v>
       </c>
       <c r="H331" s="6">
-        <v>900</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>275/45R21</t>
+          <t>275/45R20</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>GD275/45R21</t>
+          <t>CT275/45R20</t>
         </is>
       </c>
       <c r="D332" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E332" s="5">
         <v>0</v>
       </c>
       <c r="F332" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G332" s="5">
         <v>0</v>
       </c>
       <c r="H332" s="6">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/45R21</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -11156,39 +11156,39 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>GD275/45R21</t>
         </is>
       </c>
       <c r="D333" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E333" s="5">
         <v>0</v>
       </c>
       <c r="F333" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G333" s="5">
         <v>0</v>
       </c>
       <c r="H333" s="6">
-        <v>1300</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D334" s="5">
@@ -11204,13 +11204,13 @@
         <v>0</v>
       </c>
       <c r="H334" s="6">
-        <v>1600</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>285/35R22</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
@@ -11220,23 +11220,23 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>CT285/35R22</t>
         </is>
       </c>
       <c r="D335" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E335" s="5">
         <v>0</v>
       </c>
       <c r="F335" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G335" s="5">
         <v>0</v>
       </c>
       <c r="H335" s="6">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row outlineLevel="0" r="336">
@@ -11247,91 +11247,123 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D336" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E336" s="5">
         <v>0</v>
       </c>
       <c r="F336" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G336" s="5">
         <v>0</v>
       </c>
       <c r="H336" s="6">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D337" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E337" s="5">
         <v>0</v>
       </c>
       <c r="F337" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G337" s="5">
         <v>0</v>
       </c>
       <c r="H337" s="6">
-        <v>1700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D338" s="5">
+        <v>0</v>
+      </c>
+      <c r="E338" s="5">
+        <v>0</v>
+      </c>
+      <c r="F338" s="5">
+        <v>0</v>
+      </c>
+      <c r="G338" s="5">
+        <v>0</v>
+      </c>
+      <c r="H338" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="339">
+      <c r="A339" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B338" s="4" t="inlineStr">
+      <c r="B339" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C338" s="4" t="inlineStr">
+      <c r="C339" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D338" s="5">
+      <c r="D339" s="5">
         <v>2</v>
       </c>
-      <c r="E338" s="5">
+      <c r="E339" s="5">
         <v>2</v>
       </c>
-      <c r="F338" s="5">
-        <v>0</v>
-      </c>
-      <c r="G338" s="5">
-        <v>0</v>
-      </c>
-      <c r="H338" s="6">
+      <c r="F339" s="5">
+        <v>0</v>
+      </c>
+      <c r="G339" s="5">
+        <v>0</v>
+      </c>
+      <c r="H339" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="5">
         <v>14</v>
@@ -1377,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6">
         <v>200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" s="5">
         <v>5</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H41" s="6">
         <v>200</v>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E99" s="5">
         <v>4</v>
@@ -3681,7 +3681,7 @@
         <v>38</v>
       </c>
       <c r="G99" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6">
         <v>250</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="5">
         <v>4</v>
       </c>
       <c r="F3" s="5">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G3" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -673,7 +673,7 @@
         <v>-2</v>
       </c>
       <c r="G5" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="6">
         <v>240</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5">
         <v>4</v>
       </c>
       <c r="F8" s="5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5">
         <v>4</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F27" s="5">
         <v>8</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F41" s="5">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="G41" s="5">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H41" s="6">
         <v>200</v>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E64" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" s="5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G64" s="5">
         <v>4</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E68" s="5">
         <v>2</v>
       </c>
       <c r="F68" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G68" s="5">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E69" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G69" s="5">
         <v>2</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>42</v>
       </c>
       <c r="E99" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G99" s="5">
         <v>0</v>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="D159" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E159" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F159" s="5">
         <v>12</v>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="D191" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E191" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F191" s="5">
         <v>0</v>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="D227" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E227" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F227" s="5">
         <v>8</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5">
         <v>-2</v>
@@ -1380,7 +1380,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="6">
-        <v>200</v>
+        <v>215</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="D42" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E50" s="5">
         <v>4</v>
       </c>
       <c r="F50" s="5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G50" s="5">
         <v>4</v>
@@ -2139,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="E51" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F51" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G51" s="5">
         <v>4</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E64" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F64" s="5">
         <v>70</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" s="5">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G89" s="5">
         <v>4</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E94" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5">
         <v>14</v>
@@ -4795,13 +4795,13 @@
         <v>27</v>
       </c>
       <c r="E134" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5">
         <v>16</v>
       </c>
       <c r="G134" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H134" s="6">
         <v>265</v>
@@ -5787,13 +5787,13 @@
         <v>2</v>
       </c>
       <c r="E165" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
         <v>-4</v>
       </c>
       <c r="G165" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H165" s="6">
         <v>550</v>
@@ -7771,13 +7771,13 @@
         <v>10</v>
       </c>
       <c r="E227" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F227" s="5">
         <v>8</v>
       </c>
       <c r="G227" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H227" s="6">
         <v>350</v>
@@ -9659,13 +9659,13 @@
         <v>6</v>
       </c>
       <c r="E286" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
       </c>
       <c r="G286" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H286" s="6">
         <v>680</v>
@@ -9787,13 +9787,13 @@
         <v>5</v>
       </c>
       <c r="E290" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F290" s="5">
         <v>-4</v>
       </c>
       <c r="G290" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H290" s="6">
         <v>620</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D146" s="5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5">
         <v>1</v>
@@ -7224,16 +7224,16 @@
         </is>
       </c>
       <c r="D210" s="5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E210" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F210" s="5">
         <v>-4</v>
       </c>
       <c r="G210" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H210" s="6">
         <v>480</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E146" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F146" s="5">
         <v>1</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
@@ -609,7 +609,7 @@
         <v>-2</v>
       </c>
       <c r="G3" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6">
         <v>180</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="D16" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5">
         <v>2</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6">
         <v>280</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="5">
         <v>21</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24" s="6">
         <v>240</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6">
         <v>190</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E27" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F27" s="5">
         <v>8</v>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E28" s="5">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>-1</v>
       </c>
       <c r="G28" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6">
         <v>190</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="6">
         <v>210</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="6">
         <v>230</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E41" s="5">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>-11</v>
       </c>
       <c r="G41" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H41" s="6">
         <v>200</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5">
         <v>14</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5">
         <v>2</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6">
         <v>210</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="D58" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E58" s="5">
         <v>3</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6">
         <v>230</v>
@@ -2488,16 +2488,16 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E62" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5">
         <v>76</v>
       </c>
       <c r="G62" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
         <v>245</v>
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E64" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F64" s="5">
         <v>70</v>
       </c>
       <c r="G64" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="6">
         <v>280</v>
@@ -2718,10 +2718,10 @@
         <v>8</v>
       </c>
       <c r="F69" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G69" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6">
         <v>230</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" s="5">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6">
         <v>240</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E77" s="5">
         <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G77" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
         <v>290</v>
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E84" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G84" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H84" s="6">
         <v>370</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" s="5">
         <v>5</v>
@@ -3361,7 +3361,7 @@
         <v>-2</v>
       </c>
       <c r="G89" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="6">
         <v>250</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95" s="5">
         <v>4</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H95" s="6">
         <v>260</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="D98" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="5">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H98" s="6">
         <v>230</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E100" s="5">
         <v>4</v>
@@ -3713,7 +3713,7 @@
         <v>-9</v>
       </c>
       <c r="G100" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H100" s="6">
         <v>240</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E114" s="5">
         <v>4</v>
@@ -4161,7 +4161,7 @@
         <v>5</v>
       </c>
       <c r="G114" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H114" s="6">
         <v>450</v>
@@ -4318,10 +4318,10 @@
         <v>8</v>
       </c>
       <c r="F119" s="5">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H119" s="6">
         <v>480</v>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E130" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F130" s="5">
         <v>52</v>
       </c>
       <c r="G130" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H130" s="6">
         <v>290</v>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E131" s="5">
         <v>6</v>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H131" s="6">
         <v>280</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E134" s="5">
         <v>2</v>
@@ -4801,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="G134" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H134" s="6">
         <v>265</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E135" s="5">
         <v>5</v>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135" s="6">
         <v>250</v>
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="D149" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E149" s="5">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H149" s="6">
         <v>300</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D159" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E159" s="5">
         <v>3</v>
@@ -5601,7 +5601,7 @@
         <v>12</v>
       </c>
       <c r="G159" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H159" s="6">
         <v>400</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="D163" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E163" s="5">
         <v>0</v>
@@ -5729,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="G163" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H163" s="6">
         <v>380</v>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H177" s="6">
         <v>280</v>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="D182" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
         <v>3</v>
@@ -6337,7 +6337,7 @@
         <v>-1</v>
       </c>
       <c r="G182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="6">
         <v>580</v>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="D188" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E188" s="5">
         <v>4</v>
       </c>
       <c r="F188" s="5">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="G188" s="5">
         <v>2</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="D193" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5">
         <v>3</v>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="G193" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H193" s="6">
         <v>370</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="D222" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E222" s="5">
         <v>3</v>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H222" s="6">
         <v>350</v>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="D223" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E223" s="5">
         <v>4</v>
@@ -7649,7 +7649,7 @@
         <v>18</v>
       </c>
       <c r="G223" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H223" s="6">
         <v>400</v>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="D227" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E227" s="5">
         <v>0</v>
@@ -7777,7 +7777,7 @@
         <v>8</v>
       </c>
       <c r="G227" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H227" s="6">
         <v>350</v>
@@ -8216,10 +8216,10 @@
         </is>
       </c>
       <c r="D241" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E241" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F241" s="5">
         <v>15</v>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="D280" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E280" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F280" s="5">
         <v>0</v>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="D326" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" s="5">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="G326" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" s="6">
         <v>490</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="D327" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E327" s="5">
         <v>0</v>
@@ -10977,7 +10977,7 @@
         <v>0</v>
       </c>
       <c r="G327" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H327" s="6">
         <v>490</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5">
         <v>-2</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5">
         <v>2</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E27" s="5">
         <v>7</v>
@@ -1377,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6">
         <v>215</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" s="5">
         <v>26</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="D132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="D135" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E135" s="5">
         <v>5</v>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="6">
         <v>250</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G3" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E8" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
         <v>22</v>
@@ -1083,10 +1083,10 @@
         <v>8</v>
       </c>
       <c r="E18" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
         <v>4</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1368,16 +1368,16 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6">
         <v>215</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6">
         <v>230</v>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E44" s="5">
         <v>2</v>
       </c>
       <c r="F44" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E49" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G49" s="5">
         <v>2</v>
@@ -2491,13 +2491,13 @@
         <v>82</v>
       </c>
       <c r="E62" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F62" s="5">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6">
         <v>245</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D63" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -2555,13 +2555,13 @@
         <v>79</v>
       </c>
       <c r="E64" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F64" s="5">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G64" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6">
         <v>280</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E66" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>2</v>
       </c>
       <c r="F68" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G68" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H68" s="6">
         <v>250</v>
@@ -2712,16 +2712,16 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E69" s="5">
         <v>8</v>
       </c>
       <c r="F69" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G69" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="6">
         <v>230</v>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" s="5">
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6">
         <v>380</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E84" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G84" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H84" s="6">
         <v>370</v>
@@ -3358,10 +3358,10 @@
         <v>5</v>
       </c>
       <c r="F89" s="5">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G89" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" s="6">
         <v>250</v>
@@ -3422,10 +3422,10 @@
         <v>4</v>
       </c>
       <c r="F91" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G91" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H91" s="6">
         <v>370</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E94" s="5">
         <v>3</v>
@@ -3521,7 +3521,7 @@
         <v>14</v>
       </c>
       <c r="G94" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H94" s="6">
         <v>280</v>
@@ -4152,16 +4152,16 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E114" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G114" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H114" s="6">
         <v>450</v>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E130" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5">
         <v>52</v>
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="D134" s="5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E134" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G134" s="5">
         <v>6</v>
@@ -5211,13 +5211,13 @@
         <v>5</v>
       </c>
       <c r="E147" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H147" s="6">
         <v>350</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="D178" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
         <v>2</v>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H178" s="6">
         <v>480</v>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="D185" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E185" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>5</v>
       </c>
       <c r="F210" s="5">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="G210" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H210" s="6">
         <v>480</v>
@@ -7646,10 +7646,10 @@
         <v>4</v>
       </c>
       <c r="F223" s="5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G223" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H223" s="6">
         <v>400</v>
@@ -7771,10 +7771,10 @@
         <v>8</v>
       </c>
       <c r="E227" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F227" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G227" s="5">
         <v>0</v>
@@ -9656,10 +9656,10 @@
         </is>
       </c>
       <c r="D286" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E286" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
@@ -10328,10 +10328,10 @@
         </is>
       </c>
       <c r="D307" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
@@ -609,7 +609,7 @@
         <v>-4</v>
       </c>
       <c r="G3" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -763,10 +763,10 @@
         <v>26</v>
       </c>
       <c r="E8" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5">
         <v>4</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" s="5">
         <v>4</v>
@@ -1377,7 +1377,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H27" s="6">
         <v>215</v>
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E41" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" s="5">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="G41" s="5">
         <v>14</v>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E54" s="5">
         <v>2</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6">
         <v>230</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E62" s="5">
         <v>8</v>
@@ -2497,7 +2497,7 @@
         <v>70</v>
       </c>
       <c r="G62" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
         <v>245</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E64" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F64" s="5">
         <v>66</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" s="5">
         <v>2</v>
@@ -2689,7 +2689,7 @@
         <v>5</v>
       </c>
       <c r="G68" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" s="6">
         <v>250</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" s="5">
         <v>5</v>
@@ -3361,7 +3361,7 @@
         <v>-3</v>
       </c>
       <c r="G89" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="6">
         <v>250</v>
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E94" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F94" s="5">
         <v>14</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F100" s="5">
         <v>-9</v>
@@ -4344,16 +4344,16 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G120" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="6">
         <v>400</v>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E131" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
@@ -4911,28 +4911,28 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>HK205/55R17</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E138" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
       </c>
       <c r="G138" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>390</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,28 +4943,28 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E139" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
       </c>
       <c r="G139" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" s="6">
-        <v>350</v>
+        <v>390</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
@@ -4975,19 +4975,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>WL205/55R17</t>
+          <t>RD205/55R17</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E140" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -4996,23 +4996,23 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>AM205/60R16</t>
+          <t>WL205/55R17</t>
         </is>
       </c>
       <c r="D141" s="5">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>BFGOODRICH</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>BF205/60R16</t>
+          <t>AM205/60R16</t>
         </is>
       </c>
       <c r="D142" s="5">
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>320</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
@@ -5071,19 +5071,19 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>BFGOODRICH</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>BR205/60R16</t>
+          <t>BF205/60R16</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E143" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>380</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>DS205/60R16</t>
+          <t>BR205/60R16</t>
         </is>
       </c>
       <c r="D144" s="5">
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>260</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>DS205/60R16</t>
         </is>
       </c>
       <c r="D145" s="5">
@@ -5156,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>330</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
@@ -5167,28 +5167,28 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E146" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
@@ -5199,28 +5199,28 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D147" s="5">
         <v>5</v>
       </c>
       <c r="E147" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>LS205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>LS205/60R16</t>
         </is>
       </c>
       <c r="D149" s="5">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>RD205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D150" s="5">
@@ -5316,27 +5316,27 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>RD205/60R16</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E151" s="5">
         <v>0</v>
@@ -5345,30 +5345,30 @@
         <v>0</v>
       </c>
       <c r="G151" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E152" s="5">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="G152" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H152" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
@@ -5391,19 +5391,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E153" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,30 +5412,30 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>205/70R15C</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>RD205/70R15C</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E154" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,39 +5444,39 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/70R15C</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>RD205/70R15C</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E155" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F155" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G155" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>600</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,44 +5487,44 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E156" s="5">
         <v>4</v>
       </c>
       <c r="F156" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G156" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D157" s="5">
@@ -5540,13 +5540,13 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
@@ -5583,25 +5583,25 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E159" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H159" s="6">
         <v>400</v>
@@ -5615,28 +5615,28 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H160" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
@@ -5647,19 +5647,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>LS215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E161" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>360</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
@@ -5679,19 +5679,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>LS215/45R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E162" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
@@ -5711,28 +5711,28 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E163" s="5">
         <v>0</v>
       </c>
       <c r="F163" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
@@ -5743,60 +5743,60 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>RD215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D164" s="5">
+        <v>3</v>
+      </c>
+      <c r="E164" s="5">
+        <v>0</v>
+      </c>
+      <c r="F164" s="5">
         <v>1</v>
       </c>
-      <c r="E164" s="5">
-        <v>1</v>
-      </c>
-      <c r="F164" s="5">
-        <v>0</v>
-      </c>
       <c r="G164" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>RD215/45R17</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>550</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
@@ -5807,51 +5807,51 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>RD215/45R18</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>RD215/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E167" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5871,28 +5871,28 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
       </c>
       <c r="G168" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,28 +5903,28 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E169" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
       </c>
       <c r="G169" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H169" s="6">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,28 +5935,28 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E170" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
       </c>
       <c r="G170" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H170" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>RD215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,30 +5988,30 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>RD215/50R17</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R18</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,30 +6052,30 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>550</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>HK215/50R18</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F174" s="5">
         <v>0</v>
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>440</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
@@ -6095,19 +6095,19 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
@@ -6127,19 +6127,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>HK215/55R16</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
@@ -6159,16 +6159,16 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>RD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
@@ -6177,42 +6177,42 @@
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>RD215/55R16</t>
         </is>
       </c>
       <c r="D178" s="5">
         <v>2</v>
       </c>
       <c r="E178" s="5">
+        <v>0</v>
+      </c>
+      <c r="F178" s="5">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5">
         <v>2</v>
       </c>
-      <c r="F178" s="5">
-        <v>0</v>
-      </c>
-      <c r="G178" s="5">
-        <v>0</v>
-      </c>
       <c r="H178" s="6">
-        <v>480</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
@@ -6223,28 +6223,28 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="E179" s="5">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
       </c>
       <c r="G179" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>460</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R17</t>
         </is>
       </c>
       <c r="D180" s="5">
@@ -6276,7 +6276,7 @@
         <v>2</v>
       </c>
       <c r="H180" s="6">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
@@ -6287,92 +6287,92 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>SP215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E181" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F181" s="5">
         <v>0</v>
       </c>
       <c r="G181" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H181" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>SP215/55R17</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E182" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F183" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
@@ -6383,19 +6383,19 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
@@ -6415,28 +6415,28 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
@@ -6447,51 +6447,51 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E186" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H186" s="6">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>DS215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F187" s="5">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
@@ -6511,28 +6511,28 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD215/60R17</t>
+          <t>DS215/60R17</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5">
         <v>4</v>
       </c>
       <c r="F188" s="5">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>520</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
@@ -6543,28 +6543,28 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R17</t>
+          <t>GD215/60R17</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5">
         <v>4</v>
       </c>
       <c r="F189" s="5">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G189" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H189" s="6">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
@@ -6575,19 +6575,19 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>HK215/60R17</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E190" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F190" s="5">
         <v>0</v>
@@ -6596,27 +6596,27 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>BR215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E191" s="5">
         <v>0</v>
@@ -6625,10 +6625,10 @@
         <v>0</v>
       </c>
       <c r="G191" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
@@ -6639,16 +6639,16 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>BR215/65R16</t>
         </is>
       </c>
       <c r="D192" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E192" s="5">
         <v>0</v>
@@ -6657,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="G192" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H192" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
@@ -6671,19 +6671,19 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E193" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
@@ -6703,19 +6703,19 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>LF215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D194" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E194" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F194" s="5">
         <v>0</v>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>RD215/65R16</t>
+          <t>LF215/65R16</t>
         </is>
       </c>
       <c r="D195" s="5">
@@ -6756,30 +6756,30 @@
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R17</t>
+          <t>RD215/65R16</t>
         </is>
       </c>
       <c r="D196" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E196" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F196" s="5">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>480</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
@@ -6799,19 +6799,19 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R17</t>
         </is>
       </c>
       <c r="D197" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E197" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F197" s="5">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="6">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
@@ -6831,19 +6831,19 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>NX215/65R17</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D198" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" s="5">
         <v>0</v>
@@ -6852,23 +6852,23 @@
         <v>0</v>
       </c>
       <c r="H198" s="6">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>215/70R15</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15</t>
+          <t>NX215/65R17</t>
         </is>
       </c>
       <c r="D199" s="5">
@@ -6884,23 +6884,23 @@
         <v>0</v>
       </c>
       <c r="H199" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/70R15</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>AM215/70R15C</t>
+          <t>RD215/70R15</t>
         </is>
       </c>
       <c r="D200" s="5">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>BM215/70R15C</t>
+          <t>AM215/70R15C</t>
         </is>
       </c>
       <c r="D201" s="5">
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="202">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>DS215/70R15C</t>
+          <t>BM215/70R15C</t>
         </is>
       </c>
       <c r="D202" s="5">
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>DS215/70R15C</t>
         </is>
       </c>
       <c r="D203" s="5">
@@ -7012,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="H203" s="6">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="204">
@@ -7023,28 +7023,28 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>MC215/70R15C</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D204" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E204" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F204" s="5">
         <v>0</v>
       </c>
       <c r="G204" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H204" s="6">
-        <v>600</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
@@ -7055,28 +7055,28 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>OVASION</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>OV215/70R15C</t>
+          <t>MC215/70R15C</t>
         </is>
       </c>
       <c r="D205" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E205" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F205" s="5">
         <v>0</v>
       </c>
       <c r="G205" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H205" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="206">
@@ -7087,16 +7087,16 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>OVASION</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>OV215/70R15C</t>
         </is>
       </c>
       <c r="D206" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E206" s="5">
         <v>0</v>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H206" s="6">
         <v>380</v>
@@ -7119,28 +7119,28 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>SP215/70R15C</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D207" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E207" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F207" s="5">
         <v>0</v>
       </c>
       <c r="G207" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H207" s="6">
-        <v>490</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
@@ -7151,44 +7151,44 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>WL215/70R15C</t>
+          <t>SP215/70R15C</t>
         </is>
       </c>
       <c r="D208" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E208" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F208" s="5">
         <v>0</v>
       </c>
       <c r="G208" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H208" s="6">
-        <v>380</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>WL215/70R15C</t>
         </is>
       </c>
       <c r="D209" s="5">
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="H209" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
@@ -7215,28 +7215,28 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D210" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E210" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F210" s="5">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G210" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H210" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
@@ -7247,28 +7247,28 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D211" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F211" s="5">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G211" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H211" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
@@ -7279,19 +7279,19 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D212" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E212" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F212" s="5">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="H212" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D213" s="5">
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="H213" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
@@ -7343,19 +7343,19 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D214" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E214" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F214" s="5">
         <v>0</v>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
@@ -7375,83 +7375,83 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>RD225/40R18</t>
         </is>
       </c>
       <c r="D215" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E215" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F215" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G215" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H215" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D216" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E216" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F216" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G216" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H216" s="6">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>225/40R19</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R19</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D217" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E217" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F217" s="5">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="H217" s="6">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
@@ -7471,19 +7471,19 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>RD225/40R19</t>
+          <t>NX225/40R19</t>
         </is>
       </c>
       <c r="D218" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E218" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
@@ -7492,30 +7492,30 @@
         <v>0</v>
       </c>
       <c r="H218" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>225/40R19RF</t>
+          <t>225/40R19</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R19RF</t>
+          <t>RD225/40R19</t>
         </is>
       </c>
       <c r="D219" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" s="5">
         <v>0</v>
@@ -7524,30 +7524,30 @@
         <v>0</v>
       </c>
       <c r="H219" s="6">
-        <v>1200</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>BR225/45R17</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D220" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" s="5">
         <v>0</v>
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>400</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>BR225/45R17</t>
         </is>
       </c>
       <c r="D221" s="5">
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="6">
-        <v>440</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
@@ -7599,28 +7599,28 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D222" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E222" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F222" s="5">
         <v>0</v>
       </c>
       <c r="G222" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H222" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
@@ -7631,28 +7631,28 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D223" s="5">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E223" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F223" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G223" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H223" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
@@ -7663,28 +7663,28 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D224" s="5">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E224" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F224" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G224" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H224" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
@@ -7695,19 +7695,19 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>LAUFFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D225" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E225" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="5">
         <v>0</v>
@@ -7716,7 +7716,7 @@
         <v>0</v>
       </c>
       <c r="H225" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
@@ -7727,19 +7727,19 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LAUFFEN</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>RD225/45R17</t>
+          <t>LF225/45R17</t>
         </is>
       </c>
       <c r="D226" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F226" s="5">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="6">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
@@ -7759,28 +7759,28 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>SP225/45R17</t>
+          <t>RD225/45R17</t>
         </is>
       </c>
       <c r="D227" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E227" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F227" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G227" s="5">
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>350</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R17</t>
+          <t>SP225/45R17</t>
         </is>
       </c>
       <c r="D228" s="5">
@@ -7806,45 +7806,45 @@
         <v>4</v>
       </c>
       <c r="F228" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G228" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H228" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>WL225/45R17</t>
         </is>
       </c>
       <c r="D229" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E229" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F229" s="5">
         <v>0</v>
       </c>
       <c r="G229" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H229" s="6">
-        <v>500</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D230" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E230" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F230" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G230" s="5">
         <v>0</v>
       </c>
       <c r="H230" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
@@ -7887,28 +7887,28 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D231" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E231" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F231" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G231" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H231" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D232" s="5">
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
@@ -7951,19 +7951,19 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>NX225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D233" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E233" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F233" s="5">
         <v>0</v>
@@ -7972,30 +7972,30 @@
         <v>0</v>
       </c>
       <c r="H233" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>NX225/45R18</t>
         </is>
       </c>
       <c r="D234" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E234" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" s="5">
         <v>0</v>
@@ -8004,30 +8004,30 @@
         <v>0</v>
       </c>
       <c r="H234" s="6">
-        <v>720</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D235" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235" s="5">
         <v>0</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="H235" s="6">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
@@ -8047,28 +8047,28 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D236" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E236" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F236" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H236" s="6">
-        <v>750</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
@@ -8079,28 +8079,28 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D237" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E237" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F237" s="5">
         <v>0</v>
       </c>
       <c r="G237" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H237" s="6">
-        <v>520</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
@@ -8111,19 +8111,19 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>RD225/45R19</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D238" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E238" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F238" s="5">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="6">
-        <v>400</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
@@ -8143,19 +8143,19 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>WL225/45R19</t>
+          <t>RD225/45R19</t>
         </is>
       </c>
       <c r="D239" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E239" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F239" s="5">
         <v>0</v>
@@ -8164,30 +8164,30 @@
         <v>0</v>
       </c>
       <c r="H239" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>WL225/45R19</t>
         </is>
       </c>
       <c r="D240" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E240" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F240" s="5">
         <v>0</v>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="H240" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
@@ -8207,28 +8207,28 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D241" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E241" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G241" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H241" s="6">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
@@ -8239,48 +8239,48 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D242" s="5">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E242" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F242" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G242" s="5">
         <v>3</v>
       </c>
       <c r="H242" s="6">
-        <v>425</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D243" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E243" s="5">
         <v>3</v>
@@ -8289,33 +8289,33 @@
         <v>0</v>
       </c>
       <c r="G243" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H243" s="6">
-        <v>450</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>RD225/50R17</t>
         </is>
       </c>
       <c r="D244" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E244" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F244" s="5">
         <v>0</v>
@@ -8324,30 +8324,30 @@
         <v>0</v>
       </c>
       <c r="H244" s="6">
-        <v>420</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D245" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E245" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F245" s="5">
         <v>0</v>
@@ -8356,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="H245" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D246" s="5">
@@ -8388,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="H246" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
@@ -8399,19 +8399,19 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>BR225/55R17</t>
         </is>
       </c>
       <c r="D247" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E247" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F247" s="5">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="H247" s="6">
-        <v>430</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
@@ -8431,19 +8431,19 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>RD225/55R17</t>
+          <t>GD225/55R17</t>
         </is>
       </c>
       <c r="D248" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F248" s="5">
         <v>0</v>
@@ -8452,62 +8452,62 @@
         <v>0</v>
       </c>
       <c r="H248" s="6">
-        <v>360</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D249" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E249" s="5">
         <v>4</v>
       </c>
       <c r="F249" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G249" s="5">
         <v>0</v>
       </c>
       <c r="H249" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>RD225/55R17</t>
         </is>
       </c>
       <c r="D250" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F250" s="5">
         <v>0</v>
@@ -8516,62 +8516,62 @@
         <v>0</v>
       </c>
       <c r="H250" s="6">
-        <v>500</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D251" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E251" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F251" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G251" s="5">
         <v>0</v>
       </c>
       <c r="H251" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D252" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F252" s="5">
         <v>0</v>
@@ -8580,30 +8580,30 @@
         <v>0</v>
       </c>
       <c r="H252" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D253" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E253" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F253" s="5">
         <v>0</v>
@@ -8612,7 +8612,7 @@
         <v>0</v>
       </c>
       <c r="H253" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="254">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D254" s="5">
@@ -8644,62 +8644,62 @@
         <v>0</v>
       </c>
       <c r="H254" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>225/60R16</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>BR225/60R16</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D255" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E255" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F255" s="5">
         <v>0</v>
       </c>
       <c r="G255" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H255" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>225/60R16</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R16</t>
+          <t>HK225/55R19</t>
         </is>
       </c>
       <c r="D256" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F256" s="5">
         <v>0</v>
@@ -8708,27 +8708,27 @@
         <v>0</v>
       </c>
       <c r="H256" s="6">
-        <v>350</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R16</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>BR225/60R16</t>
         </is>
       </c>
       <c r="D257" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E257" s="5">
         <v>0</v>
@@ -8737,42 +8737,42 @@
         <v>0</v>
       </c>
       <c r="G257" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H257" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R16</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>RD225/60R16</t>
         </is>
       </c>
       <c r="D258" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E258" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F258" s="5">
         <v>0</v>
       </c>
       <c r="G258" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H258" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="259">
@@ -8783,19 +8783,19 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>LF225/60R17</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D259" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F259" s="5">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="H259" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="260">
@@ -8815,44 +8815,44 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>RD225/60R17</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D260" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E260" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F260" s="5">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G260" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H260" s="6">
-        <v>300</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>LF225/60R17</t>
         </is>
       </c>
       <c r="D261" s="5">
@@ -8868,13 +8868,13 @@
         <v>0</v>
       </c>
       <c r="H261" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -8884,14 +8884,14 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/60R17</t>
         </is>
       </c>
       <c r="D262" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E262" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F262" s="5">
         <v>0</v>
@@ -8900,68 +8900,68 @@
         <v>0</v>
       </c>
       <c r="H262" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D263" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" s="5">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="F263" s="5">
         <v>0</v>
       </c>
       <c r="G263" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H263" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D264" s="5">
         <v>3</v>
       </c>
       <c r="E264" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F264" s="5">
         <v>0</v>
       </c>
       <c r="G264" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H264" s="6">
         <v>450</v>
@@ -8970,39 +8970,39 @@
     <row outlineLevel="0" r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D265" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E265" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F265" s="5">
         <v>0</v>
       </c>
       <c r="G265" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H265" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>225/75R16C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -9012,11 +9012,11 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>SP225/75R16C</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D266" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E266" s="5">
         <v>0</v>
@@ -9025,16 +9025,16 @@
         <v>0</v>
       </c>
       <c r="G266" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H266" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -9044,46 +9044,46 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D267" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E267" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F267" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G267" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/75R16C</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>SP225/75R16C</t>
         </is>
       </c>
       <c r="D268" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E268" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F268" s="5">
         <v>0</v>
@@ -9092,45 +9092,45 @@
         <v>0</v>
       </c>
       <c r="H268" s="6">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>235/45R17</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R17</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D269" s="5">
         <v>4</v>
       </c>
       <c r="E269" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F269" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G269" s="5">
         <v>0</v>
       </c>
       <c r="H269" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D270" s="5">
@@ -9156,13 +9156,13 @@
         <v>0</v>
       </c>
       <c r="H270" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/45R17</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -9172,14 +9172,14 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>HK235/45R18</t>
+          <t>HK235/45R17</t>
         </is>
       </c>
       <c r="D271" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E271" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F271" s="5">
         <v>0</v>
@@ -9188,30 +9188,30 @@
         <v>0</v>
       </c>
       <c r="H271" s="6">
-        <v>500</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D272" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E272" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F272" s="5">
         <v>0</v>
@@ -9220,30 +9220,30 @@
         <v>0</v>
       </c>
       <c r="H272" s="6">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/45R18</t>
         </is>
       </c>
       <c r="D273" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E273" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F273" s="5">
         <v>0</v>
@@ -9252,62 +9252,62 @@
         <v>0</v>
       </c>
       <c r="H273" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D274" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E274" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F274" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G274" s="5">
         <v>0</v>
       </c>
       <c r="H274" s="6">
-        <v>1180</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D275" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F275" s="5">
         <v>0</v>
@@ -9316,62 +9316,62 @@
         <v>0</v>
       </c>
       <c r="H275" s="6">
-        <v>450</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D276" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E276" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F276" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G276" s="5">
         <v>0</v>
       </c>
       <c r="H276" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D277" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E277" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F277" s="5">
         <v>0</v>
@@ -9380,30 +9380,30 @@
         <v>0</v>
       </c>
       <c r="H277" s="6">
-        <v>520</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R18</t>
+          <t>HK235/55R17</t>
         </is>
       </c>
       <c r="D278" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E278" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F278" s="5">
         <v>0</v>
@@ -9412,30 +9412,30 @@
         <v>0</v>
       </c>
       <c r="H278" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D279" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E279" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F279" s="5">
         <v>0</v>
@@ -9444,30 +9444,30 @@
         <v>0</v>
       </c>
       <c r="H279" s="6">
-        <v>750</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>RD235/55R18</t>
         </is>
       </c>
       <c r="D280" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E280" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" s="5">
         <v>0</v>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="H280" s="6">
-        <v>630</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="281">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D281" s="5">
@@ -9508,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="H281" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="282">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D282" s="5">
@@ -9540,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="H282" s="6">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="283">
@@ -9551,19 +9551,19 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D283" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E283" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F283" s="5">
         <v>0</v>
@@ -9572,30 +9572,30 @@
         <v>0</v>
       </c>
       <c r="H283" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D284" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E284" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F284" s="5">
         <v>0</v>
@@ -9604,33 +9604,33 @@
         <v>0</v>
       </c>
       <c r="H284" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D285" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E285" s="5">
         <v>0</v>
       </c>
       <c r="F285" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G285" s="5">
         <v>0</v>
@@ -9642,39 +9642,39 @@
     <row outlineLevel="0" r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D286" s="5">
         <v>2</v>
       </c>
       <c r="E286" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F286" s="5">
         <v>0</v>
       </c>
       <c r="G286" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H286" s="6">
-        <v>680</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -9684,78 +9684,78 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D287" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E287" s="5">
         <v>0</v>
       </c>
       <c r="F287" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G287" s="5">
         <v>0</v>
       </c>
       <c r="H287" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>235/65R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>HK235/65R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D288" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E288" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F288" s="5">
         <v>0</v>
       </c>
       <c r="G288" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H288" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D289" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" s="5">
         <v>0</v>
@@ -9764,62 +9764,62 @@
         <v>0</v>
       </c>
       <c r="H289" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/65R17</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/65R17</t>
         </is>
       </c>
       <c r="D290" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E290" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F290" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G290" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H290" s="6">
-        <v>620</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D291" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E291" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F291" s="5">
         <v>0</v>
@@ -9828,55 +9828,55 @@
         <v>0</v>
       </c>
       <c r="H291" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D292" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E292" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F292" s="5">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="G292" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H292" s="6">
-        <v>1050</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>NX245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D293" s="5">
@@ -9892,62 +9892,62 @@
         <v>0</v>
       </c>
       <c r="H293" s="6">
-        <v>580</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D294" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E294" s="5">
         <v>0</v>
       </c>
       <c r="F294" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G294" s="5">
         <v>0</v>
       </c>
       <c r="H294" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R18</t>
+          <t>NX245/40R20</t>
         </is>
       </c>
       <c r="D295" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E295" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F295" s="5">
         <v>0</v>
@@ -9956,30 +9956,30 @@
         <v>0</v>
       </c>
       <c r="H295" s="6">
-        <v>600</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D296" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F296" s="5">
         <v>0</v>
@@ -9988,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="H296" s="6">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="297">
@@ -9999,19 +9999,19 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>BR245/45R18</t>
         </is>
       </c>
       <c r="D297" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E297" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F297" s="5">
         <v>0</v>
@@ -10031,19 +10031,19 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D298" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E298" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F298" s="5">
         <v>0</v>
@@ -10052,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="H298" s="6">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="299">
@@ -10063,44 +10063,44 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>LS245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D299" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E299" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F299" s="5">
         <v>0</v>
       </c>
       <c r="G299" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H299" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D300" s="5">
@@ -10116,27 +10116,27 @@
         <v>0</v>
       </c>
       <c r="H300" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>LS245/45R18</t>
         </is>
       </c>
       <c r="D301" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" s="5">
         <v>0</v>
@@ -10145,26 +10145,26 @@
         <v>0</v>
       </c>
       <c r="G301" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" s="6">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D302" s="5">
@@ -10180,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="H302" s="6">
-        <v>650</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="303">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D303" s="5">
@@ -10212,13 +10212,13 @@
         <v>0</v>
       </c>
       <c r="H303" s="6">
-        <v>450</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>HK245/45R19</t>
         </is>
       </c>
       <c r="D304" s="5">
@@ -10244,27 +10244,27 @@
         <v>0</v>
       </c>
       <c r="H304" s="6">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D305" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E305" s="5">
         <v>0</v>
@@ -10273,26 +10273,26 @@
         <v>0</v>
       </c>
       <c r="G305" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H305" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D306" s="5">
@@ -10308,27 +10308,27 @@
         <v>0</v>
       </c>
       <c r="H306" s="6">
-        <v>570</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>WL245/70R16</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D307" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E307" s="5">
         <v>0</v>
@@ -10337,26 +10337,26 @@
         <v>0</v>
       </c>
       <c r="G307" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H307" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D308" s="5">
@@ -10372,30 +10372,30 @@
         <v>0</v>
       </c>
       <c r="H308" s="6">
-        <v>700</v>
+        <v>570</v>
       </c>
     </row>
     <row outlineLevel="0" r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>MT255/35R19</t>
+          <t>WL245/70R16</t>
         </is>
       </c>
       <c r="D309" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E309" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F309" s="5">
         <v>0</v>
@@ -10404,23 +10404,23 @@
         <v>0</v>
       </c>
       <c r="H309" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D310" s="5">
@@ -10436,23 +10436,23 @@
         <v>0</v>
       </c>
       <c r="H310" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>MT255/35R19</t>
         </is>
       </c>
       <c r="D311" s="5">
@@ -10468,23 +10468,23 @@
         <v>0</v>
       </c>
       <c r="H311" s="6">
-        <v>1150</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>255/40R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>GD255/40R20</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D312" s="5">
@@ -10500,30 +10500,30 @@
         <v>0</v>
       </c>
       <c r="H312" s="6">
-        <v>1080</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>255/45R18</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>HK255/45R18</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D313" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E313" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" s="5">
         <v>0</v>
@@ -10532,77 +10532,77 @@
         <v>0</v>
       </c>
       <c r="H313" s="6">
-        <v>500</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/40R20</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/40R20</t>
         </is>
       </c>
       <c r="D314" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E314" s="5">
         <v>0</v>
       </c>
       <c r="F314" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G314" s="5">
         <v>0</v>
       </c>
       <c r="H314" s="6">
-        <v>750</v>
+        <v>1080</v>
       </c>
     </row>
     <row outlineLevel="0" r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/45R18</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>HK255/45R18</t>
         </is>
       </c>
       <c r="D315" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E315" s="5">
         <v>0</v>
       </c>
       <c r="F315" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G315" s="5">
         <v>0</v>
       </c>
       <c r="H315" s="6">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D316" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E316" s="5">
         <v>0</v>
       </c>
       <c r="F316" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G316" s="5">
         <v>0</v>
@@ -10634,49 +10634,49 @@
     <row outlineLevel="0" r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D317" s="5">
         <v>2</v>
       </c>
       <c r="E317" s="5">
+        <v>0</v>
+      </c>
+      <c r="F317" s="5">
         <v>2</v>
       </c>
-      <c r="F317" s="5">
-        <v>0</v>
-      </c>
       <c r="G317" s="5">
         <v>0</v>
       </c>
       <c r="H317" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D318" s="5">
@@ -10692,30 +10692,30 @@
         <v>0</v>
       </c>
       <c r="H318" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D319" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E319" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F319" s="5">
         <v>0</v>
@@ -10724,23 +10724,23 @@
         <v>0</v>
       </c>
       <c r="H319" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>WL255/70R16</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D320" s="5">
@@ -10762,24 +10762,24 @@
     <row outlineLevel="0" r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D321" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E321" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F321" s="5">
         <v>0</v>
@@ -10788,45 +10788,45 @@
         <v>0</v>
       </c>
       <c r="H321" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>WL255/70R16</t>
         </is>
       </c>
       <c r="D322" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E322" s="5">
         <v>0</v>
       </c>
       <c r="F322" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G322" s="5">
         <v>0</v>
       </c>
       <c r="H322" s="6">
-        <v>1150</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -10836,55 +10836,55 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>GD265/65R17</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D323" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E323" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F323" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G323" s="5">
         <v>0</v>
       </c>
       <c r="H323" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>LS265/65R17</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D324" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E324" s="5">
         <v>0</v>
       </c>
       <c r="F324" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G324" s="5">
         <v>0</v>
       </c>
       <c r="H324" s="6">
-        <v>650</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="325">
@@ -10895,44 +10895,44 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>NX265/65R17</t>
+          <t>GD265/65R17</t>
         </is>
       </c>
       <c r="D325" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E325" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F325" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G325" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H325" s="6">
-        <v>680</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>GR265/70R16</t>
+          <t>LS265/65R17</t>
         </is>
       </c>
       <c r="D326" s="5">
@@ -10948,62 +10948,62 @@
         <v>0</v>
       </c>
       <c r="H326" s="6">
-        <v>490</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>265/70R16</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>RD265/70R16</t>
+          <t>NX265/65R17</t>
         </is>
       </c>
       <c r="D327" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E327" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F327" s="5">
         <v>0</v>
       </c>
       <c r="G327" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H327" s="6">
-        <v>490</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GR265/70R16</t>
         </is>
       </c>
       <c r="D328" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E328" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F328" s="5">
         <v>0</v>
@@ -11012,141 +11012,141 @@
         <v>0</v>
       </c>
       <c r="H328" s="6">
-        <v>1300</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/70R16</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>RD265/70R16</t>
         </is>
       </c>
       <c r="D329" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E329" s="5">
         <v>0</v>
       </c>
       <c r="F329" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G329" s="5">
         <v>0</v>
       </c>
       <c r="H329" s="6">
-        <v>980</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D330" s="5">
         <v>2</v>
       </c>
       <c r="E330" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F330" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G330" s="5">
         <v>0</v>
       </c>
       <c r="H330" s="6">
-        <v>770</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D331" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E331" s="5">
         <v>0</v>
       </c>
       <c r="F331" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G331" s="5">
         <v>0</v>
       </c>
       <c r="H331" s="6">
-        <v>1200</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D332" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E332" s="5">
         <v>0</v>
       </c>
       <c r="F332" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G332" s="5">
         <v>0</v>
       </c>
       <c r="H332" s="6">
-        <v>900</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>275/45R21</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
@@ -11156,39 +11156,39 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>GD275/45R21</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D333" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E333" s="5">
         <v>0</v>
       </c>
       <c r="F333" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G333" s="5">
         <v>0</v>
       </c>
       <c r="H333" s="6">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/45R20</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/45R20</t>
         </is>
       </c>
       <c r="D334" s="5">
@@ -11204,109 +11204,109 @@
         <v>0</v>
       </c>
       <c r="H334" s="6">
-        <v>1300</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/45R21</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/45R21</t>
         </is>
       </c>
       <c r="D335" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E335" s="5">
         <v>0</v>
       </c>
       <c r="F335" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G335" s="5">
         <v>0</v>
       </c>
       <c r="H335" s="6">
-        <v>1600</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D336" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E336" s="5">
         <v>0</v>
       </c>
       <c r="F336" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G336" s="5">
         <v>0</v>
       </c>
       <c r="H336" s="6">
-        <v>1100</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>285/35R22</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT285/35R22</t>
         </is>
       </c>
       <c r="D337" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E337" s="5">
         <v>0</v>
       </c>
       <c r="F337" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G337" s="5">
         <v>0</v>
       </c>
       <c r="H337" s="6">
-        <v>900</v>
+        <v>1600</v>
       </c>
     </row>
     <row outlineLevel="0" r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
@@ -11316,54 +11316,118 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D338" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E338" s="5">
         <v>0</v>
       </c>
       <c r="F338" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G338" s="5">
         <v>0</v>
       </c>
       <c r="H338" s="6">
-        <v>1700</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D339" s="5">
+        <v>3</v>
+      </c>
+      <c r="E339" s="5">
+        <v>0</v>
+      </c>
+      <c r="F339" s="5">
+        <v>3</v>
+      </c>
+      <c r="G339" s="5">
+        <v>0</v>
+      </c>
+      <c r="H339" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="340">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D340" s="5">
+        <v>0</v>
+      </c>
+      <c r="E340" s="5">
+        <v>0</v>
+      </c>
+      <c r="F340" s="5">
+        <v>0</v>
+      </c>
+      <c r="G340" s="5">
+        <v>0</v>
+      </c>
+      <c r="H340" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B339" s="4" t="inlineStr">
+      <c r="B341" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C339" s="4" t="inlineStr">
+      <c r="C341" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D339" s="5">
+      <c r="D341" s="5">
         <v>2</v>
       </c>
-      <c r="E339" s="5">
+      <c r="E341" s="5">
         <v>2</v>
       </c>
-      <c r="F339" s="5">
-        <v>0</v>
-      </c>
-      <c r="G339" s="5">
-        <v>0</v>
-      </c>
-      <c r="H339" s="6">
+      <c r="F341" s="5">
+        <v>0</v>
+      </c>
+      <c r="G341" s="5">
+        <v>0</v>
+      </c>
+      <c r="H341" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="D227" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E227" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F227" s="5">
         <v>0</v>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>230</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
@@ -609,7 +609,7 @@
         <v>-4</v>
       </c>
       <c r="G3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E10" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5">
         <v>9</v>
@@ -1374,10 +1374,10 @@
         <v>4</v>
       </c>
       <c r="F27" s="5">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G27" s="5">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6">
         <v>215</v>
@@ -2488,16 +2488,16 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E62" s="5">
         <v>8</v>
       </c>
       <c r="F62" s="5">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6">
         <v>245</v>
@@ -2718,10 +2718,10 @@
         <v>8</v>
       </c>
       <c r="F69" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G69" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H69" s="6">
         <v>230</v>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="D228" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E228" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F228" s="5">
         <v>4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
@@ -609,7 +609,7 @@
         <v>-4</v>
       </c>
       <c r="G3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -670,10 +670,10 @@
         <v>4</v>
       </c>
       <c r="F5" s="5">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="6">
         <v>240</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G10" s="5">
         <v>4</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="6">
         <v>200</v>
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5">
         <v>4</v>
       </c>
       <c r="F27" s="5">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G27" s="5">
         <v>4</v>
@@ -1406,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="5">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G28" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="6">
         <v>190</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="D34" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5">
         <v>0</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G40" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" s="6">
         <v>250</v>
@@ -1915,10 +1915,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E49" s="5">
         <v>4</v>
@@ -2081,7 +2081,7 @@
         <v>-6</v>
       </c>
       <c r="G49" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H49" s="6">
         <v>210</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E62" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5">
         <v>66</v>
@@ -2939,10 +2939,10 @@
         <v>11</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G76" s="5">
         <v>7</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E77" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F77" s="5">
         <v>63</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E79" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F79" s="5">
         <v>-4</v>
@@ -3195,10 +3195,10 @@
         <v>22</v>
       </c>
       <c r="E84" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F84" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G84" s="5">
         <v>4</v>
@@ -3451,10 +3451,10 @@
         <v>5</v>
       </c>
       <c r="E92" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92" s="5">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>16</v>
       </c>
       <c r="E94" s="5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G94" s="5">
         <v>3</v>
@@ -3707,13 +3707,13 @@
         <v>-4</v>
       </c>
       <c r="E100" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="G100" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H100" s="6">
         <v>240</v>
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E106" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F106" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G106" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="6">
         <v>430</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E114" s="5">
+        <v>3</v>
+      </c>
+      <c r="F114" s="5">
         <v>2</v>
-      </c>
-      <c r="F114" s="5">
-        <v>4</v>
       </c>
       <c r="G114" s="5">
         <v>4</v>
@@ -4667,10 +4667,10 @@
         <v>63</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F130" s="5">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G130" s="5">
         <v>9</v>
@@ -4699,10 +4699,10 @@
         <v>5</v>
       </c>
       <c r="E131" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F131" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G131" s="5">
         <v>3</v>
@@ -5208,16 +5208,16 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E147" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F147" s="5">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="G147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H147" s="6">
         <v>380</v>
@@ -6363,10 +6363,10 @@
         <v>2</v>
       </c>
       <c r="E183" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F183" s="5">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
@@ -6456,16 +6456,16 @@
         </is>
       </c>
       <c r="D186" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E186" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F186" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G186" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H186" s="6">
         <v>360</v>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="D194" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E194" s="5">
         <v>3</v>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="G194" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H194" s="6">
         <v>370</v>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="D224" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E224" s="5">
         <v>4</v>
@@ -7681,7 +7681,7 @@
         <v>15</v>
       </c>
       <c r="G224" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H224" s="6">
         <v>400</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="D229" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E229" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F229" s="5">
         <v>0</v>
@@ -10235,10 +10235,10 @@
         <v>0</v>
       </c>
       <c r="E304" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F304" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G304" s="5">
         <v>0</v>
@@ -11416,10 +11416,10 @@
         </is>
       </c>
       <c r="D341" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E341" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F341" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5211,13 +5211,13 @@
         <v>3</v>
       </c>
       <c r="E147" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F147" s="5">
         <v>-3</v>
       </c>
       <c r="G147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H147" s="6">
         <v>380</v>
@@ -5243,13 +5243,13 @@
         <v>1</v>
       </c>
       <c r="E148" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
       </c>
       <c r="G148" s="5">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H148" s="6">
         <v>350</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D21" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>4</v>
       </c>
       <c r="F27" s="5">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H27" s="6">
         <v>215</v>
@@ -3518,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="F94" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G94" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6">
         <v>280</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
         <v>-3</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="D229" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E229" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F229" s="5">
         <v>0</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="D243" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E243" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F243" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="D304" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E304" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F304" s="5">
         <v>-4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E76" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
         <v>-1</v>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E84" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5">
         <v>12</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E106" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
         <v>-4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -827,10 +827,10 @@
         <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5">
         <v>4</v>
@@ -1915,10 +1915,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -3515,10 +3515,10 @@
         <v>16</v>
       </c>
       <c r="E94" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G94" s="5">
         <v>4</v>
@@ -3707,10 +3707,10 @@
         <v>-4</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="5">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="G100" s="5">
         <v>6</v>
@@ -4155,10 +4155,10 @@
         <v>9</v>
       </c>
       <c r="E114" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114" s="5">
         <v>4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>-4</v>
+        <v>18</v>
       </c>
       <c r="E100" s="5">
         <v>8</v>
       </c>
       <c r="F100" s="5">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="G100" s="5">
         <v>6</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="D100" s="5">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E100" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G100" s="5">
         <v>6</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" s="5">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="D150" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E150" s="5">
         <v>0</v>
@@ -5313,10 +5313,10 @@
         <v>0</v>
       </c>
       <c r="G150" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H150" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="D211" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E211" s="5">
         <v>5</v>
@@ -7265,7 +7265,7 @@
         <v>-8</v>
       </c>
       <c r="G211" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H211" s="6">
         <v>480</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5">
         <v>3</v>
       </c>
       <c r="F3" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5">
         <v>4</v>
       </c>
       <c r="F8" s="5">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G8" s="5">
         <v>4</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5">
         <v>4</v>
       </c>
       <c r="F10" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" s="5">
         <v>4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="D5" s="5">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
       </c>
       <c r="F5" s="5">
-        <v>-3</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E18" s="5">
         <v>4</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G18" s="5">
         <v>4</v>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E24" s="5">
         <v>21</v>
       </c>
       <c r="F24" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G24" s="5">
         <v>8</v>
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="D27" s="5">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E27" s="5">
         <v>4</v>
       </c>
       <c r="F27" s="5">
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="G27" s="5">
         <v>8</v>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="D40" s="5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E40" s="5">
         <v>4</v>
       </c>
       <c r="F40" s="5">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="G40" s="5">
         <v>6</v>
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E41" s="5">
         <v>9</v>
       </c>
       <c r="F41" s="5">
-        <v>-16</v>
+        <v>21</v>
       </c>
       <c r="G41" s="5">
         <v>14</v>
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="D44" s="5">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E44" s="5">
         <v>4</v>
       </c>
       <c r="F44" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G44" s="5">
         <v>2</v>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E46" s="5">
         <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5">
         <v>1</v>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="D49" s="5">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E49" s="5">
         <v>4</v>
       </c>
       <c r="F49" s="5">
-        <v>-6</v>
+        <v>27</v>
       </c>
       <c r="G49" s="5">
         <v>6</v>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="D50" s="5">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E50" s="5">
         <v>3</v>
       </c>
       <c r="F50" s="5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G50" s="5">
         <v>4</v>
@@ -2136,13 +2136,13 @@
         </is>
       </c>
       <c r="D51" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E51" s="5">
         <v>4</v>
       </c>
       <c r="F51" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5">
         <v>4</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E69" s="5">
         <v>8</v>
       </c>
       <c r="F69" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G69" s="5">
         <v>8</v>
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="D76" s="5">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E76" s="5">
         <v>4</v>
       </c>
       <c r="F76" s="5">
-        <v>-1</v>
+        <v>41</v>
       </c>
       <c r="G76" s="5">
         <v>7</v>
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="D79" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E79" s="5">
         <v>7</v>
       </c>
       <c r="F79" s="5">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="5">
         <v>4</v>
@@ -3096,13 +3096,13 @@
         </is>
       </c>
       <c r="D81" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E81" s="5">
         <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G81" s="5">
         <v>4</v>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="D84" s="5">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E84" s="5">
         <v>4</v>
       </c>
       <c r="F84" s="5">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G84" s="5">
         <v>4</v>
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="D89" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E89" s="5">
         <v>5</v>
       </c>
       <c r="F89" s="5">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G89" s="5">
         <v>3</v>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D94" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E94" s="5">
         <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G94" s="5">
         <v>4</v>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="D95" s="5">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E95" s="5">
         <v>4</v>
       </c>
       <c r="F95" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G95" s="5">
         <v>5</v>
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E106" s="5">
         <v>4</v>
       </c>
       <c r="F106" s="5">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="G106" s="5">
         <v>1</v>
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="D113" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E113" s="5">
         <v>1</v>
       </c>
       <c r="F113" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G113" s="5">
         <v>0</v>
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="D119" s="5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E119" s="5">
         <v>8</v>
       </c>
       <c r="F119" s="5">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="G119" s="5">
         <v>4</v>
@@ -4344,13 +4344,13 @@
         </is>
       </c>
       <c r="D120" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E120" s="5">
         <v>4</v>
       </c>
       <c r="F120" s="5">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="G120" s="5">
         <v>2</v>
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="E130" s="5">
         <v>6</v>
       </c>
       <c r="F130" s="5">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G130" s="5">
         <v>9</v>
@@ -4696,13 +4696,13 @@
         </is>
       </c>
       <c r="D131" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E131" s="5">
         <v>8</v>
       </c>
       <c r="F131" s="5">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5">
         <v>3</v>
@@ -4952,13 +4952,13 @@
         </is>
       </c>
       <c r="D139" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E139" s="5">
         <v>5</v>
       </c>
       <c r="F139" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G139" s="5">
         <v>2</v>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
         <v>4</v>
       </c>
       <c r="F147" s="5">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
@@ -5912,13 +5912,13 @@
         </is>
       </c>
       <c r="D169" s="5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E169" s="5">
         <v>4</v>
       </c>
       <c r="F169" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G169" s="5">
         <v>2</v>
@@ -6264,13 +6264,13 @@
         </is>
       </c>
       <c r="D180" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E180" s="5">
         <v>4</v>
       </c>
       <c r="F180" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G180" s="5">
         <v>2</v>
@@ -6296,13 +6296,13 @@
         </is>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E181" s="5">
         <v>4</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" s="5">
         <v>2</v>
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="D183" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E183" s="5">
         <v>4</v>
       </c>
       <c r="F183" s="5">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
@@ -6456,13 +6456,13 @@
         </is>
       </c>
       <c r="D186" s="5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E186" s="5">
         <v>4</v>
       </c>
       <c r="F186" s="5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G186" s="5">
         <v>8</v>
@@ -6552,13 +6552,13 @@
         </is>
       </c>
       <c r="D189" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E189" s="5">
         <v>4</v>
       </c>
       <c r="F189" s="5">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="G189" s="5">
         <v>2</v>
@@ -7256,13 +7256,13 @@
         </is>
       </c>
       <c r="D211" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E211" s="5">
         <v>5</v>
       </c>
       <c r="F211" s="5">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="G211" s="5">
         <v>3</v>
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="D224" s="5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E224" s="5">
         <v>4</v>
       </c>
       <c r="F224" s="5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G224" s="5">
         <v>5</v>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="D229" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E229" s="5">
         <v>2</v>
       </c>
       <c r="F229" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G229" s="5">
         <v>4</v>
@@ -7896,13 +7896,13 @@
         </is>
       </c>
       <c r="D231" s="5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E231" s="5">
         <v>4</v>
       </c>
       <c r="F231" s="5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="G231" s="5">
         <v>2</v>
@@ -8824,13 +8824,13 @@
         </is>
       </c>
       <c r="D260" s="5">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E260" s="5">
         <v>4</v>
       </c>
       <c r="F260" s="5">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="G260" s="5">
         <v>4</v>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="D292" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E292" s="5">
         <v>4</v>
       </c>
       <c r="F292" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G292" s="5">
         <v>5</v>
@@ -10232,13 +10232,13 @@
         </is>
       </c>
       <c r="D304" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E304" s="5">
         <v>8</v>
       </c>
       <c r="F304" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G304" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D148" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E148" s="5">
         <v>5</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H148" s="6">
         <v>350</v>
@@ -5816,13 +5816,13 @@
         </is>
       </c>
       <c r="D166" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E166" s="5">
         <v>4</v>
       </c>
       <c r="F166" s="5">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G166" s="5">
         <v>2</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E62" s="5">
         <v>6</v>
       </c>
       <c r="F62" s="5">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G62" s="5">
         <v>4</v>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="D64" s="5">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E64" s="5">
         <v>8</v>
       </c>
       <c r="F64" s="5">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G64" s="5">
         <v>4</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="D68" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5">
         <v>2</v>
       </c>
       <c r="F68" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G68" s="5">
         <v>2</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="D77" s="5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E77" s="5">
         <v>3</v>
       </c>
       <c r="F77" s="5">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G77" s="5">
         <v>4</v>
@@ -3416,13 +3416,13 @@
         </is>
       </c>
       <c r="D91" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E91" s="5">
         <v>4</v>
       </c>
       <c r="F91" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G91" s="5">
         <v>4</v>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="D92" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5">
         <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5">
         <v>0</v>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E99" s="5">
         <v>5</v>
       </c>
       <c r="F99" s="5">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G99" s="5">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="D160" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E160" s="5">
         <v>3</v>
       </c>
       <c r="F160" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G160" s="5">
         <v>2</v>
@@ -7256,13 +7256,13 @@
         </is>
       </c>
       <c r="D211" s="5">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E211" s="5">
         <v>5</v>
       </c>
       <c r="F211" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G211" s="5">
         <v>3</v>
@@ -8248,13 +8248,13 @@
         </is>
       </c>
       <c r="D242" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E242" s="5">
         <v>2</v>
       </c>
       <c r="F242" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G242" s="5">
         <v>3</v>
@@ -9336,13 +9336,13 @@
         </is>
       </c>
       <c r="D276" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E276" s="5">
         <v>0</v>
       </c>
       <c r="F276" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G276" s="5">
         <v>0</v>
@@ -10616,13 +10616,13 @@
         </is>
       </c>
       <c r="D316" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E316" s="5">
         <v>0</v>
       </c>
       <c r="F316" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G316" s="5">
         <v>0</v>
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="D317" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E317" s="5">
         <v>0</v>
       </c>
       <c r="F317" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G317" s="5">
         <v>0</v>
@@ -11352,13 +11352,13 @@
         </is>
       </c>
       <c r="D339" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E339" s="5">
         <v>0</v>
       </c>
       <c r="F339" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G339" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1787,10 +1787,10 @@
         <v>20</v>
       </c>
       <c r="E40" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G40" s="5">
         <v>6</v>
@@ -2555,10 +2555,10 @@
         <v>67</v>
       </c>
       <c r="E64" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G64" s="5">
         <v>4</v>
@@ -2715,10 +2715,10 @@
         <v>24</v>
       </c>
       <c r="E69" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G69" s="5">
         <v>8</v>
@@ -2939,10 +2939,10 @@
         <v>52</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G76" s="5">
         <v>7</v>
@@ -5915,10 +5915,10 @@
         <v>20</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F169" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G169" s="5">
         <v>2</v>
@@ -7835,10 +7835,10 @@
         <v>9</v>
       </c>
       <c r="E229" s="5">
+        <v>3</v>
+      </c>
+      <c r="F229" s="5">
         <v>2</v>
-      </c>
-      <c r="F229" s="5">
-        <v>3</v>
       </c>
       <c r="G229" s="5">
         <v>4</v>
@@ -8827,10 +8827,10 @@
         <v>19</v>
       </c>
       <c r="E260" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F260" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G260" s="5">
         <v>4</v>
